--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_23sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_23sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F3B9A9-E22B-4065-B0BB-08600D832467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5274B1EF-A794-43EE-8B72-4FED7B313623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1616,6 +1616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P984"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1677,7 +1678,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
@@ -1716,7 +1717,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
@@ -1755,7 +1756,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>46281.416666666664</v>
       </c>
@@ -1803,7 +1804,7 @@
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -1842,7 +1843,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
@@ -1879,7 +1880,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>46281.416666666664</v>
       </c>
@@ -1927,7 +1928,7 @@
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6" t="s">
         <v>62</v>
       </c>
@@ -1966,7 +1967,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="9" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -2005,7 +2006,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="10" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
@@ -2044,7 +2045,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="11" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="12" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
@@ -2120,7 +2121,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="13" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2157,7 +2158,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="14" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
@@ -2194,7 +2195,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="15" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>62</v>
       </c>
@@ -2233,7 +2234,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="16" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2270,7 +2271,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="17" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>46254.375</v>
       </c>
@@ -2311,7 +2312,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="18" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>46287.375</v>
       </c>
@@ -2359,7 +2360,7 @@
       <c r="O18" s="10"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
         <v>62</v>
       </c>
@@ -2396,7 +2397,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6" t="s">
         <v>62</v>
       </c>
@@ -2435,7 +2436,7 @@
       <c r="O20"/>
       <c r="P20"/>
     </row>
-    <row r="21" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>46288.480219907404</v>
       </c>
@@ -2481,7 +2482,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
@@ -2520,7 +2521,7 @@
       <c r="O22"/>
       <c r="P22"/>
     </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
         <v>62</v>
       </c>
@@ -2559,7 +2560,7 @@
       <c r="O23"/>
       <c r="P23"/>
     </row>
-    <row r="24" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -2607,7 +2608,7 @@
       <c r="O24"/>
       <c r="P24"/>
     </row>
-    <row r="25" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>62</v>
       </c>
@@ -2648,7 +2649,7 @@
       <c r="O25"/>
       <c r="P25"/>
     </row>
-    <row r="26" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
         <v>62</v>
       </c>
@@ -2687,7 +2688,7 @@
       <c r="O26"/>
       <c r="P26"/>
     </row>
-    <row r="27" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
         <v>62</v>
       </c>
@@ -2726,7 +2727,7 @@
       <c r="O27"/>
       <c r="P27"/>
     </row>
-    <row r="28" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -2767,7 +2768,7 @@
       <c r="O28"/>
       <c r="P28"/>
     </row>
-    <row r="29" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
         <v>62</v>
       </c>
@@ -2806,7 +2807,7 @@
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>46121.375</v>
       </c>
@@ -2855,7 +2856,7 @@
       <c r="O30"/>
       <c r="P30"/>
     </row>
-    <row r="31" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
         <v>62</v>
       </c>
@@ -2894,7 +2895,7 @@
       <c r="O31"/>
       <c r="P31"/>
     </row>
-    <row r="32" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>46286.527083333334</v>
       </c>
@@ -2940,7 +2941,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>62</v>
       </c>
@@ -2981,7 +2982,7 @@
       <c r="O33"/>
       <c r="P33"/>
     </row>
-    <row r="34" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
         <v>62</v>
       </c>
@@ -3022,7 +3023,7 @@
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
@@ -3061,7 +3062,7 @@
       <c r="O35"/>
       <c r="P35"/>
     </row>
-    <row r="36" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>62</v>
       </c>
@@ -3101,7 +3102,7 @@
       </c>
       <c r="O36"/>
     </row>
-    <row r="37" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
@@ -3142,7 +3143,7 @@
       <c r="O37"/>
       <c r="P37"/>
     </row>
-    <row r="38" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="6" t="s">
         <v>62</v>
       </c>
@@ -3183,7 +3184,7 @@
       <c r="O38"/>
       <c r="P38"/>
     </row>
-    <row r="39" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="6" t="s">
         <v>62</v>
       </c>
@@ -3222,7 +3223,7 @@
       <c r="O39"/>
       <c r="P39"/>
     </row>
-    <row r="40" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="6" t="s">
         <v>62</v>
       </c>
@@ -3261,7 +3262,7 @@
       <c r="O40"/>
       <c r="P40"/>
     </row>
-    <row r="41" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3">
         <v>46286.375</v>
       </c>
@@ -3308,7 +3309,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
         <v>46274.375</v>
       </c>
@@ -3354,7 +3355,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="3">
         <v>46260.375</v>
       </c>
@@ -3400,7 +3401,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3440,7 +3441,7 @@
       </c>
       <c r="P44"/>
     </row>
-    <row r="45" spans="1:16" s="26" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" s="26" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="3">
         <v>46252.6875</v>
       </c>
@@ -3481,7 +3482,7 @@
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>62</v>
       </c>
@@ -3519,7 +3520,7 @@
       </c>
       <c r="O46"/>
     </row>
-    <row r="47" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="6" t="s">
         <v>62</v>
       </c>
@@ -3557,7 +3558,7 @@
       </c>
       <c r="O47"/>
     </row>
-    <row r="48" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="3">
         <v>46286.375</v>
       </c>
@@ -3605,7 +3606,7 @@
       <c r="O48" s="10"/>
       <c r="P48" s="10"/>
     </row>
-    <row r="49" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <v>46286.375</v>
       </c>
@@ -3652,7 +3653,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="6" t="s">
         <v>62</v>
       </c>
@@ -3691,7 +3692,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="6" t="s">
         <v>62</v>
       </c>
@@ -3732,7 +3733,7 @@
       <c r="O51"/>
       <c r="P51"/>
     </row>
-    <row r="52" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
         <v>46282.416666666664</v>
       </c>
@@ -3778,7 +3779,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3819,7 +3820,7 @@
       <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="3">
         <v>46288.500671296293</v>
       </c>
@@ -3865,7 +3866,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
@@ -3906,7 +3907,7 @@
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" s="25" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" s="25" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3">
         <v>46288.569641203707</v>
       </c>
@@ -3954,7 +3955,7 @@
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
     </row>
-    <row r="57" spans="1:16" s="31" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" s="31" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="6" t="s">
         <v>62</v>
       </c>
@@ -3993,7 +3994,7 @@
       <c r="O57" s="10"/>
       <c r="P57" s="10"/>
     </row>
-    <row r="58" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3">
         <v>46268.385416666664</v>
       </c>
@@ -4039,7 +4040,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="6" t="s">
         <v>62</v>
       </c>
@@ -4078,7 +4079,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="60" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3">
         <v>46261.375</v>
       </c>
@@ -4126,7 +4127,7 @@
       <c r="O60" s="10"/>
       <c r="P60" s="25"/>
     </row>
-    <row r="61" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="3">
         <v>46283.375</v>
       </c>
@@ -4174,7 +4175,7 @@
       <c r="O61" s="10"/>
       <c r="P61" s="10"/>
     </row>
-    <row r="62" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
@@ -4213,7 +4214,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="63" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="32">
         <v>46288.375532407408</v>
       </c>
@@ -4261,7 +4262,7 @@
       <c r="O63" s="31"/>
       <c r="P63" s="31"/>
     </row>
-    <row r="64" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="32">
         <v>46288.375567129631</v>
       </c>
@@ -4309,7 +4310,7 @@
       <c r="O64" s="31"/>
       <c r="P64" s="31"/>
     </row>
-    <row r="65" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="6" t="s">
         <v>62</v>
       </c>
@@ -4348,7 +4349,7 @@
       <c r="O65" s="10"/>
       <c r="P65" s="10"/>
     </row>
-    <row r="66" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3">
         <v>46252.6875</v>
       </c>
@@ -4389,7 +4390,7 @@
       <c r="O66" s="10"/>
       <c r="P66" s="10"/>
     </row>
-    <row r="67" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
         <v>46287.375</v>
       </c>
@@ -4435,7 +4436,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="68" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>62</v>
       </c>
@@ -4476,7 +4477,7 @@
       <c r="O68" s="30"/>
       <c r="P68"/>
     </row>
-    <row r="69" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
@@ -4515,7 +4516,7 @@
       <c r="O69" s="19"/>
       <c r="P69" s="10"/>
     </row>
-    <row r="70" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3">
         <v>46261.375</v>
       </c>
@@ -4561,7 +4562,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3">
         <v>46282.443055555559</v>
       </c>
@@ -4607,7 +4608,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3">
         <v>46031.4375</v>
       </c>
@@ -4648,7 +4649,7 @@
       </c>
       <c r="P72" s="19"/>
     </row>
-    <row r="73" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="6" t="s">
         <v>62</v>
       </c>
@@ -4732,7 +4733,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="75" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="6" t="s">
         <v>62</v>
       </c>
@@ -4773,7 +4774,7 @@
       <c r="O75" s="10"/>
       <c r="P75" s="26"/>
     </row>
-    <row r="76" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
         <v>46275.457638888889</v>
       </c>
@@ -4821,7 +4822,7 @@
       <c r="O76" s="10"/>
       <c r="P76" s="10"/>
     </row>
-    <row r="77" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -4899,7 +4900,7 @@
         <v>8970</v>
       </c>
       <c r="M78" s="18">
-        <f t="shared" ref="M78:M85" si="0">ABS((D78*E78)-L78)</f>
+        <f>ABS((D78*E78)-L78)</f>
         <v>300</v>
       </c>
       <c r="N78" s="10" t="str">
@@ -4945,7 +4946,7 @@
         <v>8400</v>
       </c>
       <c r="M79" s="18">
-        <f t="shared" si="0"/>
+        <f>ABS((D79*E79)-L79)</f>
         <v>300</v>
       </c>
       <c r="N79" s="10" t="str">
@@ -4993,7 +4994,7 @@
         <v>32900</v>
       </c>
       <c r="M80" s="18">
-        <f t="shared" si="0"/>
+        <f>ABS((D80*E80)-L80)</f>
         <v>1000</v>
       </c>
       <c r="N80" s="10" t="str">
@@ -5039,7 +5040,7 @@
         <v>5585</v>
       </c>
       <c r="M81" s="29">
-        <f t="shared" si="0"/>
+        <f>ABS((D81*E81)-L81)</f>
         <v>395</v>
       </c>
       <c r="N81" s="31" t="str">
@@ -5089,7 +5090,7 @@
         <v>5730</v>
       </c>
       <c r="M82" s="29">
-        <f t="shared" si="0"/>
+        <f>ABS((D82*E82)-L82)</f>
         <v>250</v>
       </c>
       <c r="N82" s="31" t="str">
@@ -5139,7 +5140,7 @@
         <v>6367.2</v>
       </c>
       <c r="M83" s="18">
-        <f t="shared" si="0"/>
+        <f>ABS((D83*E83)-L83)</f>
         <v>300.80000000000018</v>
       </c>
       <c r="N83" s="10" t="str">
@@ -5185,7 +5186,7 @@
         <v>3005</v>
       </c>
       <c r="M84" s="18">
-        <f t="shared" si="0"/>
+        <f>ABS((D84*E84)-L84)</f>
         <v>240</v>
       </c>
       <c r="N84" s="10" t="str">
@@ -5232,7 +5233,7 @@
         <v>11660</v>
       </c>
       <c r="M85" s="18">
-        <f t="shared" si="0"/>
+        <f>ABS((D85*E85)-L85)</f>
         <v>300</v>
       </c>
       <c r="N85" s="10" t="str">
@@ -5244,7 +5245,7 @@
       </c>
       <c r="P85" s="10"/>
     </row>
-    <row r="86" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>62</v>
       </c>
@@ -5547,7 +5548,7 @@
         <v>5755</v>
       </c>
       <c r="M92" s="29">
-        <f t="shared" ref="M92:M100" si="1">ABS((D92*E92)-L92)</f>
+        <f>ABS((D92*E92)-L92)</f>
         <v>275</v>
       </c>
       <c r="N92" s="31" t="str">
@@ -5595,7 +5596,7 @@
         <v>5805</v>
       </c>
       <c r="M93" s="29">
-        <f t="shared" si="1"/>
+        <f>ABS((D93*E93)-L93)</f>
         <v>225</v>
       </c>
       <c r="N93" s="31" t="str">
@@ -5643,7 +5644,7 @@
         <v>39300</v>
       </c>
       <c r="M94" s="18">
-        <f t="shared" si="1"/>
+        <f>ABS((D94*E94)-L94)</f>
         <v>18850</v>
       </c>
       <c r="N94" s="10" t="str">
@@ -5689,7 +5690,7 @@
         <v>19730.5</v>
       </c>
       <c r="M95" s="29">
-        <f t="shared" si="1"/>
+        <f>ABS((D95*E95)-L95)</f>
         <v>504.5</v>
       </c>
       <c r="N95" s="31" t="str">
@@ -5739,7 +5740,7 @@
         <v>19690</v>
       </c>
       <c r="M96" s="29">
-        <f t="shared" si="1"/>
+        <f>ABS((D96*E96)-L96)</f>
         <v>545</v>
       </c>
       <c r="N96" s="31" t="str">
@@ -5789,7 +5790,7 @@
         <v>10400</v>
       </c>
       <c r="M97" s="18">
-        <f t="shared" si="1"/>
+        <f>ABS((D97*E97)-L97)</f>
         <v>300</v>
       </c>
       <c r="N97" s="10" t="str">
@@ -5835,7 +5836,7 @@
         <v>33200</v>
       </c>
       <c r="M98" s="18">
-        <f t="shared" si="1"/>
+        <f>ABS((D98*E98)-L98)</f>
         <v>1200</v>
       </c>
       <c r="N98" s="10" t="str">
@@ -5881,7 +5882,7 @@
         <v>4120</v>
       </c>
       <c r="M99" s="29">
-        <f t="shared" si="1"/>
+        <f>ABS((D99*E99)-L99)</f>
         <v>270</v>
       </c>
       <c r="N99" s="31" t="str">
@@ -5931,7 +5932,7 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M100" s="29">
-        <f t="shared" si="1"/>
+        <f>ABS((D100*E100)-L100)</f>
         <v>188.60000000000014</v>
       </c>
       <c r="N100" s="31" t="str">
@@ -5943,7 +5944,7 @@
       </c>
       <c r="P100" s="31"/>
     </row>
-    <row r="101" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6" t="s">
         <v>62</v>
       </c>
@@ -6512,7 +6513,7 @@
         <v>8700</v>
       </c>
       <c r="M113" s="18">
-        <f t="shared" ref="M113:M122" si="2">ABS((D113*E113)-L113)</f>
+        <f>ABS((D113*E113)-L113)</f>
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
@@ -6558,7 +6559,7 @@
         <v>4852</v>
       </c>
       <c r="M114" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D114*E114)-L114)</f>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
@@ -6604,7 +6605,7 @@
         <v>5905</v>
       </c>
       <c r="M115" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D115*E115)-L115)</f>
         <v>275</v>
       </c>
       <c r="N115" t="str">
@@ -6650,7 +6651,7 @@
         <v>10249</v>
       </c>
       <c r="M116" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D116*E116)-L116)</f>
         <v>4451</v>
       </c>
       <c r="N116" s="10" t="str">
@@ -6699,7 +6700,7 @@
         <v>39300</v>
       </c>
       <c r="M117" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D117*E117)-L117)</f>
         <v>18350</v>
       </c>
       <c r="N117" s="10" t="str">
@@ -6745,7 +6746,7 @@
         <v>3400</v>
       </c>
       <c r="M118" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D118*E118)-L118)</f>
         <v>250</v>
       </c>
       <c r="N118" s="10" t="str">
@@ -6791,7 +6792,7 @@
         <v>8480</v>
       </c>
       <c r="M119" s="27">
-        <f t="shared" si="2"/>
+        <f>ABS((D119*E119)-L119)</f>
         <v>280</v>
       </c>
       <c r="N119" t="str">
@@ -6840,7 +6841,7 @@
         <v>15075</v>
       </c>
       <c r="M120" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D120*E120)-L120)</f>
         <v>645</v>
       </c>
       <c r="N120" s="10" t="str">
@@ -6889,7 +6890,7 @@
         <v>8420</v>
       </c>
       <c r="M121" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D121*E121)-L121)</f>
         <v>300</v>
       </c>
       <c r="N121" s="10" t="str">
@@ -6937,7 +6938,7 @@
         <v>14440</v>
       </c>
       <c r="M122" s="18">
-        <f t="shared" si="2"/>
+        <f>ABS((D122*E122)-L122)</f>
         <v>300</v>
       </c>
       <c r="N122" s="10" t="str">
@@ -7459,7 +7460,7 @@
         <v>26109.000000000004</v>
       </c>
       <c r="M134" s="29">
-        <f t="shared" ref="M134:M145" si="3">ABS((D134*E134)-L134)</f>
+        <f>ABS((D134*E134)-L134)</f>
         <v>710.99999999999636</v>
       </c>
       <c r="N134" s="10" t="str">
@@ -7507,7 +7508,7 @@
         <v>16500</v>
       </c>
       <c r="M135" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D135*E135)-L135)</f>
         <v>1400</v>
       </c>
       <c r="N135" s="10" t="str">
@@ -7557,7 +7558,7 @@
         <v>10300</v>
       </c>
       <c r="M136" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D136*E136)-L136)</f>
         <v>300</v>
       </c>
       <c r="N136" s="10" t="str">
@@ -7604,7 +7605,7 @@
         <v>10814</v>
       </c>
       <c r="M137" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D137*E137)-L137)</f>
         <v>501</v>
       </c>
       <c r="N137" s="10" t="str">
@@ -7653,7 +7654,7 @@
         <v>5370</v>
       </c>
       <c r="M138" s="29">
-        <f t="shared" si="3"/>
+        <f>ABS((D138*E138)-L138)</f>
         <v>320</v>
       </c>
       <c r="N138" s="31" t="str">
@@ -7701,7 +7702,7 @@
         <v>2610</v>
       </c>
       <c r="M139" s="29">
-        <f t="shared" si="3"/>
+        <f>ABS((D139*E139)-L139)</f>
         <v>235</v>
       </c>
       <c r="N139" s="31" t="str">
@@ -7749,7 +7750,7 @@
         <v>73800</v>
       </c>
       <c r="M140" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D140*E140)-L140)</f>
         <v>48320</v>
       </c>
       <c r="N140" s="10" t="str">
@@ -7799,7 +7800,7 @@
         <v>9470</v>
       </c>
       <c r="M141" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D141*E141)-L141)</f>
         <v>300</v>
       </c>
       <c r="N141" s="10" t="str">
@@ -7845,7 +7846,7 @@
         <v>14200</v>
       </c>
       <c r="M142" s="18">
-        <f t="shared" si="3"/>
+        <f>ABS((D142*E142)-L142)</f>
         <v>500</v>
       </c>
       <c r="N142" s="10" t="str">
@@ -7891,7 +7892,7 @@
         <v>7578</v>
       </c>
       <c r="M143" s="29">
-        <f t="shared" si="3"/>
+        <f>ABS((D143*E143)-L143)</f>
         <v>294</v>
       </c>
       <c r="N143" s="30" t="str">
@@ -7937,7 +7938,7 @@
         <v>7578</v>
       </c>
       <c r="M144" s="29">
-        <f t="shared" si="3"/>
+        <f>ABS((D144*E144)-L144)</f>
         <v>294</v>
       </c>
       <c r="N144" s="31" t="str">
@@ -7983,7 +7984,7 @@
         <v>4968</v>
       </c>
       <c r="M145" s="29">
-        <f t="shared" si="3"/>
+        <f>ABS((D145*E145)-L145)</f>
         <v>280</v>
       </c>
       <c r="N145" s="31" t="str">
@@ -8188,7 +8189,7 @@
         <v>10410</v>
       </c>
       <c r="M150" s="18">
-        <f t="shared" ref="M150:M155" si="4">ABS((D150*E150)-L150)</f>
+        <f>ABS((D150*E150)-L150)</f>
         <v>300</v>
       </c>
       <c r="N150" s="10" t="str">
@@ -8235,7 +8236,7 @@
         <v>5520</v>
       </c>
       <c r="M151" s="29">
-        <f t="shared" si="4"/>
+        <f>ABS((D151*E151)-L151)</f>
         <v>300</v>
       </c>
       <c r="N151" s="30" t="str">
@@ -8284,7 +8285,7 @@
         <v>2657</v>
       </c>
       <c r="M152" s="29">
-        <f t="shared" si="4"/>
+        <f>ABS((D152*E152)-L152)</f>
         <v>253</v>
       </c>
       <c r="N152" s="31" t="str">
@@ -8333,7 +8334,7 @@
         <v>2554.5</v>
       </c>
       <c r="M153" s="29">
-        <f t="shared" si="4"/>
+        <f>ABS((D153*E153)-L153)</f>
         <v>355.5</v>
       </c>
       <c r="N153" s="31" t="str">
@@ -8382,7 +8383,7 @@
         <v>4080</v>
       </c>
       <c r="M154" s="18">
-        <f t="shared" si="4"/>
+        <f>ABS((D154*E154)-L154)</f>
         <v>300</v>
       </c>
       <c r="N154" s="10" t="str">
@@ -8430,7 +8431,7 @@
         <v>18140</v>
       </c>
       <c r="M155" s="27">
-        <f t="shared" si="4"/>
+        <f>ABS((D155*E155)-L155)</f>
         <v>650</v>
       </c>
       <c r="N155" t="str">
@@ -8772,7 +8773,7 @@
         <v>8049</v>
       </c>
       <c r="M163" s="18">
-        <f t="shared" ref="M163:M169" si="5">ABS((D163*E163)-L163)</f>
+        <f>ABS((D163*E163)-L163)</f>
         <v>800</v>
       </c>
       <c r="N163" s="10" t="str">
@@ -8821,7 +8822,7 @@
         <v>10510</v>
       </c>
       <c r="M164" s="18">
-        <f t="shared" si="5"/>
+        <f>ABS((D164*E164)-L164)</f>
         <v>300</v>
       </c>
       <c r="N164" s="10" t="str">
@@ -8869,7 +8870,7 @@
         <v>25300</v>
       </c>
       <c r="M165" s="18">
-        <f t="shared" si="5"/>
+        <f>ABS((D165*E165)-L165)</f>
         <v>650</v>
       </c>
       <c r="N165" s="10" t="str">
@@ -8919,7 +8920,7 @@
         <v>12480</v>
       </c>
       <c r="M166" s="18">
-        <f t="shared" si="5"/>
+        <f>ABS((D166*E166)-L166)</f>
         <v>495</v>
       </c>
       <c r="N166" s="10" t="str">
@@ -8968,7 +8969,7 @@
         <v>8820</v>
       </c>
       <c r="M167" s="29">
-        <f t="shared" si="5"/>
+        <f>ABS((D167*E167)-L167)</f>
         <v>650</v>
       </c>
       <c r="N167" s="31" t="str">
@@ -9016,7 +9017,7 @@
         <v>36946</v>
       </c>
       <c r="M168" s="29">
-        <f t="shared" si="5"/>
+        <f>ABS((D168*E168)-L168)</f>
         <v>934</v>
       </c>
       <c r="N168" s="31" t="str">
@@ -9064,7 +9065,7 @@
         <v>14172.5</v>
       </c>
       <c r="M169" s="29">
-        <f t="shared" si="5"/>
+        <f>ABS((D169*E169)-L169)</f>
         <v>527.5</v>
       </c>
       <c r="N169" s="31" t="str">
@@ -21758,6 +21759,16 @@
       <c r="I984" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P294" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="S"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P294">
+      <sortCondition ref="F1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_23sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_23sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5274B1EF-A794-43EE-8B72-4FED7B313623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A83A9A7-5E18-4451-A74C-25C7504D9BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1151,7 +1151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1311,8 +1311,69 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1678,30 +1739,30 @@
         <v>242</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4">
-        <v>660</v>
+        <v>2470</v>
       </c>
       <c r="F2" s="4">
-        <v>-29.415539280000001</v>
+        <v>3.7815126050000001</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="H2" s="5">
-        <v>935.05</v>
+        <v>2380</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
@@ -1716,37 +1777,39 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B2, $C$2:$C$712, C2, $D$2:$D$712, D2, $E$2:$E$712, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O2" s="10"/>
+      <c r="P2" s="25"/>
+    </row>
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
-        <v>2560</v>
+        <v>2435</v>
       </c>
       <c r="F3" s="4">
-        <v>-24.01306026</v>
+        <v>2.3109243699999999</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H3" s="5">
-        <v>3369</v>
+        <v>2380</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="37" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -1755,13 +1818,15 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B3, $C$2:$C$712, C3, $D$2:$D$712, D3, $E$2:$E$712, E3) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
-        <v>46281.416666666664</v>
+        <v>46252.645138888889</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>285</v>
+        <v>68</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -1770,108 +1835,112 @@
         <v>10</v>
       </c>
       <c r="E4" s="4">
-        <v>706</v>
+        <v>401</v>
       </c>
       <c r="F4" s="4">
-        <v>-22.511250140000001</v>
+        <v>0.98212037269999997</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>292</v>
+        <v>69</v>
       </c>
       <c r="H4" s="5">
-        <v>911.1</v>
+        <v>397.1</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="L4" s="18">
-        <v>17940</v>
-      </c>
-      <c r="M4" s="18">
-        <f>ABS((D4*E4)-L4)</f>
-        <v>10880</v>
-      </c>
-      <c r="N4" s="10" t="str">
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B4, $C$2:$C$712, C4, $D$2:$D$712, D4, $E$2:$E$712, E4) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
-        <v>46252.688194444447</v>
+        <v>46275.457638888889</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E5" s="4">
-        <v>136.15</v>
+        <v>222</v>
       </c>
       <c r="F5" s="4">
-        <v>-21.30057803</v>
+        <v>0.77624948930000004</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="H5" s="5">
-        <v>173</v>
+        <v>220.29</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" t="str">
+      <c r="J5" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="L5" s="18">
+        <v>56375</v>
+      </c>
+      <c r="M5" s="18">
+        <f>ABS((D5*E5)-L5)</f>
+        <v>34175</v>
+      </c>
+      <c r="N5" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B5, $C$2:$C$712, C5, $D$2:$D$712, D5, $E$2:$E$712, E5) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4">
-        <v>2660</v>
+        <v>281</v>
       </c>
       <c r="F6" s="4">
-        <v>-21.044820420000001</v>
+        <v>0.7529580495</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H6" s="5">
-        <v>3369</v>
+        <v>278.89999999999998</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="37"/>
+      <c r="J6" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
@@ -1879,203 +1948,217 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B6, $C$2:$C$712, C6, $D$2:$D$712, D6, $E$2:$E$712, E6) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
-        <v>46281.416666666664</v>
+      <c r="O6" s="10"/>
+      <c r="P6" s="26"/>
+    </row>
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>285</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4">
-        <v>726</v>
+        <v>3888</v>
       </c>
       <c r="F7" s="4">
-        <v>-20.316101419999999</v>
+        <v>-0.91743119269999995</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>292</v>
+        <v>50</v>
       </c>
       <c r="H7" s="5">
-        <v>911.1</v>
+        <v>3924</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="L7" s="18">
-        <v>17940</v>
-      </c>
-      <c r="M7" s="18">
-        <f>ABS((D7*E7)-L7)</f>
-        <v>10680</v>
-      </c>
-      <c r="N7" s="10" t="str">
+      <c r="J7" s="37"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B7, $C$2:$C$712, C7, $D$2:$D$712, D7, $E$2:$E$712, E7) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O7" s="10"/>
+      <c r="O7" s="26"/>
       <c r="P7" s="10"/>
     </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>62</v>
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>46031.4375</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>210</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="4">
-        <v>2752</v>
+        <v>1052</v>
       </c>
       <c r="F8" s="4">
-        <v>-18.314039770000001</v>
+        <v>-0.94161958570000004</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>221</v>
       </c>
       <c r="H8" s="5">
-        <v>3369</v>
+        <v>1062</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" t="str">
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18">
+        <f>ABS((D8*E8)-L8)</f>
+        <v>3156</v>
+      </c>
+      <c r="N8" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B8, $C$2:$C$712, C8, $D$2:$D$712, D8, $E$2:$E$712, E8) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
-        <v>62</v>
+      <c r="O8" s="10"/>
+      <c r="P8" s="19"/>
+    </row>
+    <row r="9" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E9" s="4">
-        <v>3914</v>
+        <v>205</v>
       </c>
       <c r="F9" s="4">
-        <v>-17.19030995</v>
+        <v>-1.157184185</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
-        <v>4726.5</v>
+        <v>207.4</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="38" t="s">
+      <c r="J9" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" t="str">
+      <c r="K9" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="L9" s="18">
+        <v>10550</v>
+      </c>
+      <c r="M9" s="18">
+        <f>ABS((D9*E9)-L9)</f>
+        <v>300</v>
+      </c>
+      <c r="N9" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B9, $C$2:$C$712, C9, $D$2:$D$712, D9, $E$2:$E$712, E9) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
+        <v>Duplicate</v>
+      </c>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
+        <v>46282.443055555559</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E10" s="4">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F10" s="4">
-        <v>-16.913946589999998</v>
+        <v>-1.157184185</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H10" s="5">
-        <v>235.9</v>
+        <v>207.4</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
+      <c r="J10" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="L10" s="18">
+        <v>10550</v>
+      </c>
+      <c r="M10" s="18">
+        <f>ABS((D10*E10)-L10)</f>
+        <v>300</v>
+      </c>
       <c r="N10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B10, $C$2:$C$712, C10, $D$2:$D$712, D10, $E$2:$E$712, E10) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>Duplicate</v>
+      </c>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>701</v>
+        <v>3856</v>
       </c>
       <c r="F11" s="4">
-        <v>-15.74519231</v>
+        <v>-1.7329255859999999</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="H11" s="5">
-        <v>832</v>
+        <v>3924</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="37" t="s">
-        <v>41</v>
-      </c>
+      <c r="J11" s="37"/>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
@@ -2083,36 +2166,40 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B11, $C$2:$C$712, C11, $D$2:$D$712, D11, $E$2:$E$712, E11) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O11" s="19"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E12" s="4">
-        <v>4014</v>
+        <v>31.01</v>
       </c>
       <c r="F12" s="4">
-        <v>-15.0745795</v>
+        <v>-1.836024058</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="H12" s="5">
-        <v>4726.5</v>
+        <v>31.59</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="37"/>
+      <c r="J12" s="37" t="s">
+        <v>55</v>
+      </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
@@ -2120,73 +2207,87 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B12, $C$2:$C$712, C12, $D$2:$D$712, D12, $E$2:$E$712, E12) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O12" s="30"/>
+    </row>
+    <row r="13" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
-        <v>46252.635416666664</v>
+        <v>46287.375</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>2892</v>
+        <v>19300</v>
       </c>
       <c r="F13" s="4">
-        <v>-14.15850401</v>
+        <v>-1.905972046</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="H13" s="5">
-        <v>3369</v>
+        <v>19675</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="37"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" t="str">
+      <c r="J13" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="L13" s="18">
+        <v>19950</v>
+      </c>
+      <c r="M13" s="18">
+        <f>ABS((D13*E13)-L13)</f>
+        <v>650</v>
+      </c>
+      <c r="N13" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B13, $C$2:$C$712, C13, $D$2:$D$712, D13, $E$2:$E$712, E13) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
-        <v>62</v>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E14" s="4">
-        <v>4164</v>
+        <v>122</v>
       </c>
       <c r="F14" s="4">
-        <v>-11.90098381</v>
+        <v>-2.2044088180000001</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H14" s="5">
-        <v>4726.5</v>
+        <v>124.75</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="37"/>
+      <c r="J14" s="38" t="s">
+        <v>41</v>
+      </c>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
@@ -2194,38 +2295,38 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B14, $C$2:$C$712, C14, $D$2:$D$712, D14, $E$2:$E$712, E14) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>561</v>
+        <v>3830</v>
       </c>
       <c r="F15" s="4">
-        <v>-11.67440762</v>
+        <v>-2.3955147810000001</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="H15" s="5">
-        <v>635.15</v>
+        <v>3924</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="37" t="s">
-        <v>41</v>
-      </c>
+      <c r="J15" s="37"/>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
@@ -2233,318 +2334,348 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B15, $C$2:$C$712, C15, $D$2:$D$712, D15, $E$2:$E$712, E15) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="32">
+        <v>46288.375532407408</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="34">
+        <v>10</v>
+      </c>
+      <c r="E16" s="34">
+        <v>887</v>
+      </c>
+      <c r="F16" s="4">
+        <v>-2.74122807</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="5">
+        <v>912</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="L16" s="29">
+        <v>9170</v>
+      </c>
+      <c r="M16" s="29">
+        <f>ABS((D16*E16)-L16)</f>
+        <v>300</v>
+      </c>
+      <c r="N16" s="31" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$712, B16, $C$2:$C$712, C16, $D$2:$D$712, D16, $E$2:$E$712, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Duplicate</v>
+      </c>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+    </row>
+    <row r="17" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="32">
+        <v>46288.375567129631</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="34">
+        <v>10</v>
+      </c>
+      <c r="E17" s="34">
+        <v>887</v>
+      </c>
+      <c r="F17" s="4">
+        <v>-2.74122807</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="5">
+        <v>912</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="L17" s="29">
+        <v>9070</v>
+      </c>
+      <c r="M17" s="29">
+        <f>ABS((D17*E17)-L17)</f>
+        <v>200</v>
+      </c>
+      <c r="N17" s="31" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$712, B17, $C$2:$C$712, C17, $D$2:$D$712, D17, $E$2:$E$712, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Duplicate</v>
+      </c>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+    </row>
+    <row r="18" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4">
-        <v>100</v>
-      </c>
-      <c r="E16" s="4">
-        <v>111</v>
-      </c>
-      <c r="F16" s="4">
-        <v>-11.02204409</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" s="5">
-        <v>124.75</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="37"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$712, B16, $C$2:$C$712, C16, $D$2:$D$712, D16, $E$2:$E$712, E16) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
-        <v>46254.375</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="4">
-        <v>7</v>
-      </c>
-      <c r="E17" s="4">
-        <v>2230</v>
-      </c>
-      <c r="F17" s="4">
-        <v>-9.898989899</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="5">
-        <v>2475</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$712, B17, $C$2:$C$712, C17, $D$2:$D$712, D17, $E$2:$E$712, E17) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3">
-        <v>46287.375</v>
-      </c>
       <c r="B18" s="1" t="s">
-        <v>295</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4">
-        <v>1564</v>
+        <v>6920</v>
       </c>
       <c r="F18" s="4">
-        <v>-9.7883140100000006</v>
+        <v>-2.7543563799999999</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>297</v>
+        <v>108</v>
       </c>
       <c r="H18" s="5">
-        <v>1733.7</v>
+        <v>7116</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="L18" s="18">
-        <v>3430</v>
-      </c>
-      <c r="M18" s="18">
-        <f>ABS((D18*E18)-L18)</f>
-        <v>302</v>
-      </c>
-      <c r="N18" s="10" t="str">
+      <c r="J18" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B18, $C$2:$C$712, C18, $D$2:$D$712, D18, $E$2:$E$712, E18) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-    </row>
-    <row r="19" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
-        <v>62</v>
+    </row>
+    <row r="19" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>46283.375</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4">
-        <v>1751</v>
+        <v>870.2</v>
       </c>
       <c r="F19" s="4">
-        <v>-9.2746113989999994</v>
+        <v>-2.7818120880000001</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="H19" s="5">
-        <v>1930</v>
+        <v>895.1</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="37"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" t="str">
+      <c r="J19" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="L19" s="18">
+        <v>17920</v>
+      </c>
+      <c r="M19" s="18">
+        <f>ABS((D19*E19)-L19)</f>
+        <v>516</v>
+      </c>
+      <c r="N19" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B19, $C$2:$C$712, C19, $D$2:$D$712, D19, $E$2:$E$712, E19) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
-        <v>62</v>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E20" s="4">
-        <v>411</v>
+        <v>870</v>
       </c>
       <c r="F20" s="4">
-        <v>-8.7275149899999995</v>
+        <v>-2.8041559600000001</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="H20" s="5">
-        <v>450.3</v>
+        <v>895.1</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="37"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" t="str">
+      <c r="J20" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="L20" s="18">
+        <v>17700</v>
+      </c>
+      <c r="M20" s="18">
+        <f>ABS((D20*E20)-L20)</f>
+        <v>300</v>
+      </c>
+      <c r="N20" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B20, $C$2:$C$712, C20, $D$2:$D$712, D20, $E$2:$E$712, E20) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O20"/>
-      <c r="P20"/>
-    </row>
-    <row r="21" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3">
-        <v>46288.480219907404</v>
+      <c r="P20" s="25"/>
+    </row>
+    <row r="21" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21" s="4">
-        <v>580</v>
+        <v>4010</v>
       </c>
       <c r="F21" s="4">
-        <v>-8.6829882699999992</v>
+        <v>-2.8043725909999999</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H21" s="5">
-        <v>635.15</v>
+        <v>4125.7</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="L21" s="18">
-        <v>3150</v>
-      </c>
-      <c r="M21" s="18">
-        <f>ABS((D21*E21)-L21)</f>
-        <v>250</v>
-      </c>
-      <c r="N21" s="10" t="str">
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B21, $C$2:$C$712, C21, $D$2:$D$712, D21, $E$2:$E$712, E21) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
-        <v>62</v>
+    <row r="22" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
+        <v>46268.385416666664</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E22" s="4">
-        <v>4415</v>
+        <v>214</v>
       </c>
       <c r="F22" s="4">
-        <v>-8.3454432220000001</v>
+        <v>-2.8553270689999999</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="H22" s="5">
-        <v>4817</v>
+        <v>220.29</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="37"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" t="str">
+      <c r="J22" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="L22" s="18">
+        <v>21900</v>
+      </c>
+      <c r="M22" s="18">
+        <f>ABS((D22*E22)-L22)</f>
+        <v>500</v>
+      </c>
+      <c r="N22" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B22, $C$2:$C$712, C22, $D$2:$D$712, D22, $E$2:$E$712, E22) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O22"/>
-      <c r="P22"/>
-    </row>
-    <row r="23" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="4">
-        <v>18052</v>
+        <v>3810</v>
       </c>
       <c r="F23" s="4">
-        <v>-8.2490470140000003</v>
+        <v>-2.9051987769999998</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="H23" s="5">
-        <v>19675</v>
+        <v>3924</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>8</v>
@@ -2557,33 +2688,31 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B23, $C$2:$C$712, C23, $D$2:$D$712, D23, $E$2:$E$712, E23) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O23"/>
-      <c r="P23"/>
-    </row>
-    <row r="24" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
-        <v>46258.601388888892</v>
+        <v>46288.569641203707</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E24" s="4">
-        <v>2271</v>
+        <v>1136</v>
       </c>
       <c r="F24" s="4">
-        <v>-8.2424242420000002</v>
+        <v>-2.9059829060000002</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="H24" s="5">
-        <v>2475</v>
+        <v>1170</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
@@ -2592,10 +2721,10 @@
         <v>55</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="L24" s="18">
-        <v>7113</v>
+        <v>11660</v>
       </c>
       <c r="M24" s="18">
         <f>ABS((D24*E24)-L24)</f>
@@ -2605,33 +2734,31 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B24, $C$2:$C$712, C24, $D$2:$D$712, D24, $E$2:$E$712, E24) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O24"/>
-      <c r="P24"/>
-    </row>
-    <row r="25" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E25" s="4">
-        <v>4364</v>
+        <v>201</v>
       </c>
       <c r="F25" s="4">
-        <v>-7.6695229029999998</v>
+        <v>-3.0858244940000001</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="H25" s="5">
-        <v>4726.5</v>
+        <v>207.4</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>8</v>
@@ -2649,74 +2776,83 @@
       <c r="O25"/>
       <c r="P25"/>
     </row>
-    <row r="26" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
-        <v>62</v>
+    <row r="26" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <v>46288.500671296293</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E26" s="4">
-        <v>115.25</v>
+        <v>321</v>
       </c>
       <c r="F26" s="4">
-        <v>-7.6152304610000003</v>
+        <v>-3.4586466169999999</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="H26" s="5">
-        <v>124.75</v>
+        <v>332.5</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="37"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" t="str">
+      <c r="J26" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="L26" s="18">
+        <v>32800</v>
+      </c>
+      <c r="M26" s="18">
+        <f>ABS((D26*E26)-L26)</f>
+        <v>700</v>
+      </c>
+      <c r="N26" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B26, $C$2:$C$712, C26, $D$2:$D$712, D26, $E$2:$E$712, E26) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O26"/>
-      <c r="P26"/>
-    </row>
-    <row r="27" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
-        <v>62</v>
+    </row>
+    <row r="27" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="4">
-        <v>4456</v>
+        <v>1302</v>
       </c>
       <c r="F27" s="4">
-        <v>-7.4942910530000004</v>
+        <v>-3.4840622680000002</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="H27" s="5">
-        <v>4817</v>
+        <v>1349</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="37"/>
+      <c r="J27" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
@@ -2727,76 +2863,83 @@
       <c r="O27"/>
       <c r="P27"/>
     </row>
-    <row r="28" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
-        <v>46252.688194444447</v>
+        <v>46282.416666666664</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="4">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E28" s="4">
-        <v>640</v>
+        <v>880</v>
       </c>
       <c r="F28" s="4">
-        <v>-7.4475777299999999</v>
+        <v>-3.50877193</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="H28" s="5">
-        <v>691.5</v>
+        <v>912</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
+      <c r="J28" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="L28" s="18">
+        <v>35920</v>
+      </c>
+      <c r="M28" s="18">
+        <f>ABS((D28*E28)-L28)</f>
+        <v>720</v>
+      </c>
       <c r="N28" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B28, $C$2:$C$712, C28, $D$2:$D$712, D28, $E$2:$E$712, E28) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O28"/>
-      <c r="P28"/>
-    </row>
-    <row r="29" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E29" s="4">
-        <v>116</v>
+        <v>1614</v>
       </c>
       <c r="F29" s="4">
-        <v>-7.0140280559999999</v>
+        <v>-3.6417910450000002</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H29" s="5">
-        <v>124.75</v>
+        <v>1675</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="37"/>
+      <c r="J29" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
@@ -2807,118 +2950,118 @@
       <c r="O29"/>
       <c r="P29"/>
     </row>
-    <row r="30" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="3">
-        <v>46121.375</v>
+    <row r="30" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E30" s="4">
-        <v>1614</v>
+        <v>212</v>
       </c>
       <c r="F30" s="4">
-        <v>-6.9794248169999999</v>
+        <v>-3.763221208</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="H30" s="5">
-        <v>1735.1</v>
+        <v>220.29</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J30" s="24" t="s">
+      <c r="J30" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="K30" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="L30" s="18">
-        <f>3*1794</f>
-        <v>5382</v>
-      </c>
-      <c r="M30" s="18">
-        <f>ABS((D30*E30)-L30)</f>
-        <v>540</v>
-      </c>
-      <c r="N30" s="10" t="str">
+      <c r="K30" s="17"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B30, $C$2:$C$712, C30, $D$2:$D$712, D30, $E$2:$E$712, E30) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O30"/>
-      <c r="P30"/>
-    </row>
-    <row r="31" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
-        <v>62</v>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+    </row>
+    <row r="31" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="3">
+        <v>46286.375</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E31" s="4">
-        <v>4410</v>
+        <v>712</v>
       </c>
       <c r="F31" s="4">
-        <v>-6.6962868929999999</v>
+        <v>-3.887688985</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="H31" s="5">
-        <v>4726.5</v>
+        <v>740.8</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="37"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" t="str">
+      <c r="J31" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="L31" s="18">
+        <f>7470/2</f>
+        <v>3735</v>
+      </c>
+      <c r="M31" s="18">
+        <f>ABS((D31*E31)-L31)</f>
+        <v>175</v>
+      </c>
+      <c r="N31" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B31, $C$2:$C$712, C31, $D$2:$D$712, D31, $E$2:$E$712, E31) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O31"/>
-      <c r="P31"/>
-    </row>
-    <row r="32" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
-        <v>46286.527083333334</v>
+        <v>46286.375</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" s="4">
-        <v>4410</v>
+        <v>1664</v>
       </c>
       <c r="F32" s="4">
-        <v>-6.6962868929999999</v>
+        <v>-4.0977465280000001</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H32" s="5">
-        <v>4726.5</v>
+        <v>1735.1</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
@@ -2927,51 +3070,49 @@
         <v>41</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L32" s="18">
-        <v>4724</v>
+        <v>8970</v>
       </c>
       <c r="M32" s="18">
         <f>ABS((D32*E32)-L32)</f>
-        <v>314</v>
+        <v>650</v>
       </c>
       <c r="N32" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B32, $C$2:$C$712, C32, $D$2:$D$712, D32, $E$2:$E$712, E32) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="4">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
-        <v>836</v>
+        <v>3760</v>
       </c>
       <c r="F33" s="4">
-        <v>-6.6026142329999997</v>
+        <v>-4.179408767</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="H33" s="5">
-        <v>895.1</v>
+        <v>3924</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="37" t="s">
-        <v>118</v>
-      </c>
+      <c r="J33" s="37"/>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
@@ -2980,14 +3121,13 @@
         <v>Unique</v>
       </c>
       <c r="O33"/>
-      <c r="P33"/>
-    </row>
-    <row r="34" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>10</v>
@@ -2996,23 +3136,21 @@
         <v>50</v>
       </c>
       <c r="E34" s="4">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="F34" s="4">
-        <v>-6.4869036270000002</v>
+        <v>-4.609218437</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="H34" s="5">
-        <v>220.29</v>
+        <v>124.75</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J34" s="37" t="s">
-        <v>41</v>
-      </c>
+      <c r="J34" s="37"/>
       <c r="K34" s="17"/>
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
@@ -3021,37 +3159,38 @@
         <v>Unique</v>
       </c>
       <c r="O34"/>
-      <c r="P34"/>
-    </row>
-    <row r="35" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="6" t="s">
-        <v>62</v>
+    </row>
+    <row r="35" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E35" s="4">
-        <v>18552</v>
+        <v>326</v>
       </c>
       <c r="F35" s="4">
-        <v>-5.7077509529999997</v>
+        <v>-4.6783625730000002</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H35" s="5">
-        <v>19675</v>
+        <v>342</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="37"/>
+      <c r="J35" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
@@ -3062,35 +3201,35 @@
       <c r="O35"/>
       <c r="P35"/>
     </row>
-    <row r="36" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="6" t="s">
-        <v>62</v>
+    <row r="36" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="4">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E36" s="4">
-        <v>401</v>
+        <v>850</v>
       </c>
       <c r="F36" s="4">
-        <v>-5.6248529070000002</v>
+        <v>-5.0385431799999996</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H36" s="5">
-        <v>424.9</v>
+        <v>895.1</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="22" t="s">
+      <c r="J36" s="38" t="s">
         <v>55</v>
       </c>
       <c r="K36" s="17"/>
@@ -3100,130 +3239,148 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B36, $C$2:$C$712, C36, $D$2:$D$712, D36, $E$2:$E$712, E36) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O36"/>
-    </row>
-    <row r="37" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
-        <v>62</v>
+      <c r="P36"/>
+    </row>
+    <row r="37" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="3">
+        <v>46260.375</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E37" s="4">
-        <v>196</v>
+        <v>2348</v>
       </c>
       <c r="F37" s="4">
-        <v>-5.4966248789999996</v>
+        <v>-5.1313131309999997</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="H37" s="5">
-        <v>207.4</v>
+        <v>2475</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="37" t="s">
+      <c r="J37" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
+      <c r="K37" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="L37" s="18">
+        <v>7344</v>
+      </c>
+      <c r="M37" s="18">
+        <f>ABS((D37*E37)-L37)</f>
+        <v>300</v>
+      </c>
       <c r="N37" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B37, $C$2:$C$712, C37, $D$2:$D$712, D37, $E$2:$E$712, E37) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O37"/>
-      <c r="P37"/>
-    </row>
-    <row r="38" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="6" t="s">
-        <v>62</v>
+    </row>
+    <row r="38" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="3">
+        <v>46274.375</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="4">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E38" s="4">
-        <v>862</v>
+        <v>1005</v>
       </c>
       <c r="F38" s="4">
-        <v>-5.48245614</v>
+        <v>-5.1886792450000003</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H38" s="5">
-        <v>912</v>
+        <v>1060</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J38" s="37" t="s">
+      <c r="J38" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" t="str">
+      <c r="K38" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="L38" s="18">
+        <v>15600</v>
+      </c>
+      <c r="M38" s="18">
+        <f>ABS((D38*E38)-L38)</f>
+        <v>525</v>
+      </c>
+      <c r="N38" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B38, $C$2:$C$712, C38, $D$2:$D$712, D38, $E$2:$E$712, E38) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O38"/>
-      <c r="P38"/>
-    </row>
-    <row r="39" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
-        <v>62</v>
+    </row>
+    <row r="39" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="3">
+        <v>46286.375</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="4">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="E39" s="4">
-        <v>1277</v>
+        <v>702</v>
       </c>
       <c r="F39" s="4">
-        <v>-5.3372868789999997</v>
+        <v>-5.237580994</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H39" s="5">
-        <v>1349</v>
+        <v>740.8</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="37"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" t="str">
+      <c r="J39" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="L39" s="18">
+        <f>7470/2</f>
+        <v>3735</v>
+      </c>
+      <c r="M39" s="18">
+        <f>ABS((D39*E39)-L39)</f>
+        <v>225</v>
+      </c>
+      <c r="N39" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B39, $C$2:$C$712, C39, $D$2:$D$712, D39, $E$2:$E$712, E39) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O39"/>
-      <c r="P39"/>
-    </row>
-    <row r="40" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="6" t="s">
         <v>62</v>
       </c>
@@ -3262,174 +3419,156 @@
       <c r="O40"/>
       <c r="P40"/>
     </row>
-    <row r="41" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="3">
-        <v>46286.375</v>
+    <row r="41" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="4">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="E41" s="4">
-        <v>702</v>
+        <v>1277</v>
       </c>
       <c r="F41" s="4">
-        <v>-5.237580994</v>
+        <v>-5.3372868789999997</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="H41" s="5">
-        <v>740.8</v>
+        <v>1349</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K41" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="L41" s="18">
-        <f>7470/2</f>
-        <v>3735</v>
-      </c>
-      <c r="M41" s="18">
-        <f>ABS((D41*E41)-L41)</f>
-        <v>225</v>
-      </c>
-      <c r="N41" s="10" t="str">
+      <c r="J41" s="37"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B41, $C$2:$C$712, C41, $D$2:$D$712, D41, $E$2:$E$712, E41) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="3">
-        <v>46274.375</v>
+      <c r="O41"/>
+      <c r="P41"/>
+    </row>
+    <row r="42" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="4">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E42" s="4">
-        <v>1005</v>
+        <v>862</v>
       </c>
       <c r="F42" s="4">
-        <v>-5.1886792450000003</v>
+        <v>-5.48245614</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H42" s="5">
-        <v>1060</v>
+        <v>912</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J42" s="24" t="s">
+      <c r="J42" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="K42" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="L42" s="18">
-        <v>15600</v>
-      </c>
-      <c r="M42" s="18">
-        <f>ABS((D42*E42)-L42)</f>
-        <v>525</v>
-      </c>
-      <c r="N42" s="10" t="str">
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B42, $C$2:$C$712, C42, $D$2:$D$712, D42, $E$2:$E$712, E42) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="3">
-        <v>46260.375</v>
+      <c r="O42"/>
+      <c r="P42"/>
+    </row>
+    <row r="43" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E43" s="4">
-        <v>2348</v>
+        <v>196</v>
       </c>
       <c r="F43" s="4">
-        <v>-5.1313131309999997</v>
+        <v>-5.4966248789999996</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H43" s="5">
-        <v>2475</v>
+        <v>207.4</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="24" t="s">
+      <c r="J43" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="K43" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="L43" s="18">
-        <v>7344</v>
-      </c>
-      <c r="M43" s="18">
-        <f>ABS((D43*E43)-L43)</f>
-        <v>300</v>
-      </c>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
       <c r="N43" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B43, $C$2:$C$712, C43, $D$2:$D$712, D43, $E$2:$E$712, E43) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="3">
-        <v>46252.635416666664</v>
+      <c r="O43"/>
+      <c r="P43"/>
+    </row>
+    <row r="44" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E44" s="4">
-        <v>850</v>
+        <v>401</v>
       </c>
       <c r="F44" s="4">
-        <v>-5.0385431799999996</v>
+        <v>-5.6248529070000002</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H44" s="5">
-        <v>895.1</v>
+        <v>424.9</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="38" t="s">
+      <c r="J44" s="22" t="s">
         <v>55</v>
       </c>
       <c r="K44" s="17"/>
@@ -3439,39 +3578,37 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B44, $C$2:$C$712, C44, $D$2:$D$712, D44, $E$2:$E$712, E44) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P44"/>
-    </row>
-    <row r="45" spans="1:16" s="26" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="3">
-        <v>46252.6875</v>
+      <c r="O44"/>
+    </row>
+    <row r="45" spans="1:16" s="26" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E45" s="4">
-        <v>326</v>
+        <v>18552</v>
       </c>
       <c r="F45" s="4">
-        <v>-4.6783625730000002</v>
+        <v>-5.7077509529999997</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H45" s="5">
-        <v>342</v>
+        <v>19675</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="37" t="s">
-        <v>41</v>
-      </c>
+      <c r="J45" s="37"/>
       <c r="K45" s="17"/>
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
@@ -3482,12 +3619,12 @@
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>10</v>
@@ -3496,21 +3633,23 @@
         <v>50</v>
       </c>
       <c r="E46" s="4">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="F46" s="4">
-        <v>-4.609218437</v>
+        <v>-6.4869036270000002</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="H46" s="5">
-        <v>124.75</v>
+        <v>220.29</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="37"/>
+      <c r="J46" s="37" t="s">
+        <v>41</v>
+      </c>
       <c r="K46" s="17"/>
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
@@ -3519,36 +3658,39 @@
         <v>Unique</v>
       </c>
       <c r="O46"/>
-    </row>
-    <row r="47" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P46"/>
+    </row>
+    <row r="47" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="4">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E47" s="4">
-        <v>3760</v>
+        <v>836</v>
       </c>
       <c r="F47" s="4">
-        <v>-4.179408767</v>
+        <v>-6.6026142329999997</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H47" s="5">
-        <v>3924</v>
+        <v>895.1</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="37"/>
+      <c r="J47" s="37" t="s">
+        <v>118</v>
+      </c>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
@@ -3557,79 +3699,71 @@
         <v>Unique</v>
       </c>
       <c r="O47"/>
-    </row>
-    <row r="48" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="3">
-        <v>46286.375</v>
+      <c r="P47"/>
+    </row>
+    <row r="48" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E48" s="4">
-        <v>1664</v>
+        <v>4410</v>
       </c>
       <c r="F48" s="4">
-        <v>-4.0977465280000001</v>
+        <v>-6.6962868929999999</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H48" s="5">
-        <v>1735.1</v>
+        <v>4726.5</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K48" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="L48" s="18">
-        <v>8970</v>
-      </c>
-      <c r="M48" s="18">
-        <f>ABS((D48*E48)-L48)</f>
-        <v>650</v>
-      </c>
-      <c r="N48" s="10" t="str">
+      <c r="J48" s="37"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B48, $C$2:$C$712, C48, $D$2:$D$712, D48, $E$2:$E$712, E48) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-    </row>
-    <row r="49" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O48"/>
+      <c r="P48"/>
+    </row>
+    <row r="49" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
-        <v>46286.375</v>
+        <v>46286.527083333334</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4">
-        <v>712</v>
+        <v>4410</v>
       </c>
       <c r="F49" s="4">
-        <v>-3.887688985</v>
+        <v>-6.6962868929999999</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="H49" s="5">
-        <v>740.8</v>
+        <v>4726.5</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>8</v>
@@ -3638,91 +3772,98 @@
         <v>41</v>
       </c>
       <c r="K49" s="18" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="L49" s="18">
-        <f>7470/2</f>
-        <v>3735</v>
+        <v>4724</v>
       </c>
       <c r="M49" s="18">
         <f>ABS((D49*E49)-L49)</f>
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="N49" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B49, $C$2:$C$712, C49, $D$2:$D$712, D49, $E$2:$E$712, E49) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="6" t="s">
-        <v>62</v>
+    <row r="50" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
+        <v>46121.375</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E50" s="4">
-        <v>212</v>
+        <v>1614</v>
       </c>
       <c r="F50" s="4">
-        <v>-3.763221208</v>
+        <v>-6.9794248169999999</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="H50" s="5">
-        <v>220.29</v>
+        <v>1735.1</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="37" t="s">
+      <c r="J50" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" t="str">
+      <c r="K50" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="L50" s="18">
+        <f>3*1794</f>
+        <v>5382</v>
+      </c>
+      <c r="M50" s="18">
+        <f>ABS((D50*E50)-L50)</f>
+        <v>540</v>
+      </c>
+      <c r="N50" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B50, $C$2:$C$712, C50, $D$2:$D$712, D50, $E$2:$E$712, E50) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O50"/>
+      <c r="P50"/>
+    </row>
+    <row r="51" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D51" s="4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E51" s="4">
-        <v>1614</v>
+        <v>116</v>
       </c>
       <c r="F51" s="4">
-        <v>-3.6417910450000002</v>
+        <v>-7.0140280559999999</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H51" s="5">
-        <v>1675</v>
+        <v>124.75</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="22" t="s">
-        <v>41</v>
-      </c>
+      <c r="J51" s="37"/>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
@@ -3733,83 +3874,76 @@
       <c r="O51"/>
       <c r="P51"/>
     </row>
-    <row r="52" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
-        <v>46282.416666666664</v>
+        <v>46252.688194444447</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="4">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E52" s="4">
-        <v>880</v>
+        <v>640</v>
       </c>
       <c r="F52" s="4">
-        <v>-3.50877193</v>
+        <v>-7.4475777299999999</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="H52" s="5">
-        <v>912</v>
+        <v>691.5</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K52" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="L52" s="18">
-        <v>35920</v>
-      </c>
-      <c r="M52" s="18">
-        <f>ABS((D52*E52)-L52)</f>
-        <v>720</v>
-      </c>
+      <c r="J52" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
       <c r="N52" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B52, $C$2:$C$712, C52, $D$2:$D$712, D52, $E$2:$E$712, E52) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="3">
-        <v>46252.635416666664</v>
+      <c r="O52"/>
+      <c r="P52"/>
+    </row>
+    <row r="53" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D53" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="4">
-        <v>1302</v>
+        <v>4456</v>
       </c>
       <c r="F53" s="4">
-        <v>-3.4840622680000002</v>
+        <v>-7.4942910530000004</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="H53" s="5">
-        <v>1349</v>
+        <v>4817</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J53" s="37" t="s">
-        <v>41</v>
-      </c>
+      <c r="J53" s="37"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
@@ -3820,76 +3954,69 @@
       <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3">
-        <v>46288.500671296293</v>
+    <row r="54" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E54" s="4">
-        <v>321</v>
+        <v>115.25</v>
       </c>
       <c r="F54" s="4">
-        <v>-3.4586466169999999</v>
+        <v>-7.6152304610000003</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H54" s="5">
-        <v>332.5</v>
+        <v>124.75</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K54" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="L54" s="18">
-        <v>32800</v>
-      </c>
-      <c r="M54" s="18">
-        <f>ABS((D54*E54)-L54)</f>
-        <v>700</v>
-      </c>
-      <c r="N54" s="10" t="str">
+      <c r="J54" s="37"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B54, $C$2:$C$712, C54, $D$2:$D$712, D54, $E$2:$E$712, E54) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O54"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E55" s="4">
-        <v>201</v>
+        <v>4364</v>
       </c>
       <c r="F55" s="4">
-        <v>-3.0858244940000001</v>
+        <v>-7.6695229029999998</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H55" s="5">
-        <v>207.4</v>
+        <v>4726.5</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>8</v>
@@ -3907,30 +4034,30 @@
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" s="25" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" s="25" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3">
-        <v>46288.569641203707</v>
+        <v>46258.601388888892</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E56" s="4">
-        <v>1136</v>
+        <v>2271</v>
       </c>
       <c r="F56" s="4">
-        <v>-2.9059829060000002</v>
+        <v>-8.2424242420000002</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="H56" s="5">
-        <v>1170</v>
+        <v>2475</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>8</v>
@@ -3939,10 +4066,10 @@
         <v>55</v>
       </c>
       <c r="K56" s="18" t="s">
-        <v>314</v>
+        <v>159</v>
       </c>
       <c r="L56" s="18">
-        <v>11660</v>
+        <v>7113</v>
       </c>
       <c r="M56" s="18">
         <f>ABS((D56*E56)-L56)</f>
@@ -3952,33 +4079,33 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B56, $C$2:$C$712, C56, $D$2:$D$712, D56, $E$2:$E$712, E56) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-    </row>
-    <row r="57" spans="1:16" s="31" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O56"/>
+      <c r="P56"/>
+    </row>
+    <row r="57" spans="1:16" s="31" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" s="4">
-        <v>3810</v>
+        <v>18052</v>
       </c>
       <c r="F57" s="4">
-        <v>-2.9051987769999998</v>
+        <v>-8.2490470140000003</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="H57" s="5">
-        <v>3924</v>
+        <v>19675</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>8</v>
@@ -3991,354 +4118,325 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B57, $C$2:$C$712, C57, $D$2:$D$712, D57, $E$2:$E$712, E57) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-    </row>
-    <row r="58" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="3">
-        <v>46268.385416666664</v>
+      <c r="O57"/>
+      <c r="P57"/>
+    </row>
+    <row r="58" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D58" s="4">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="E58" s="4">
-        <v>214</v>
+        <v>4415</v>
       </c>
       <c r="F58" s="4">
-        <v>-2.8553270689999999</v>
+        <v>-8.3454432220000001</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="H58" s="5">
-        <v>220.29</v>
+        <v>4817</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K58" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="L58" s="18">
-        <v>21900</v>
-      </c>
-      <c r="M58" s="18">
-        <f>ABS((D58*E58)-L58)</f>
-        <v>500</v>
-      </c>
-      <c r="N58" s="10" t="str">
+      <c r="J58" s="37"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B58, $C$2:$C$712, C58, $D$2:$D$712, D58, $E$2:$E$712, E58) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="6" t="s">
-        <v>62</v>
+      <c r="O58"/>
+      <c r="P58"/>
+    </row>
+    <row r="59" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="3">
+        <v>46288.480219907404</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59" s="4">
-        <v>4010</v>
+        <v>580</v>
       </c>
       <c r="F59" s="4">
-        <v>-2.8043725909999999</v>
+        <v>-8.6829882699999992</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H59" s="5">
-        <v>4125.7</v>
+        <v>635.15</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="37" t="s">
+      <c r="J59" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" t="str">
+      <c r="K59" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="L59" s="18">
+        <v>3150</v>
+      </c>
+      <c r="M59" s="18">
+        <f>ABS((D59*E59)-L59)</f>
+        <v>250</v>
+      </c>
+      <c r="N59" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B59, $C$2:$C$712, C59, $D$2:$D$712, D59, $E$2:$E$712, E59) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="60" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="3">
-        <v>46261.375</v>
+    <row r="60" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="4">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E60" s="4">
-        <v>870</v>
+        <v>411</v>
       </c>
       <c r="F60" s="4">
-        <v>-2.8041559600000001</v>
+        <v>-8.7275149899999995</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="H60" s="5">
-        <v>895.1</v>
+        <v>450.3</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K60" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="L60" s="18">
-        <v>17700</v>
-      </c>
-      <c r="M60" s="18">
-        <f>ABS((D60*E60)-L60)</f>
-        <v>300</v>
-      </c>
-      <c r="N60" s="10" t="str">
+      <c r="J60" s="72"/>
+      <c r="K60" s="17"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B60, $C$2:$C$712, C60, $D$2:$D$712, D60, $E$2:$E$712, E60) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O60" s="10"/>
-      <c r="P60" s="25"/>
-    </row>
-    <row r="61" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3">
-        <v>46283.375</v>
+    </row>
+    <row r="61" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E61" s="4">
-        <v>870.2</v>
+        <v>1751</v>
       </c>
       <c r="F61" s="4">
-        <v>-2.7818120880000001</v>
+        <v>-9.2746113989999994</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="H61" s="5">
-        <v>895.1</v>
+        <v>1930</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K61" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="L61" s="18">
-        <v>17920</v>
-      </c>
-      <c r="M61" s="18">
-        <f>ABS((D61*E61)-L61)</f>
-        <v>516</v>
-      </c>
-      <c r="N61" s="10" t="str">
+      <c r="J61" s="72"/>
+      <c r="K61" s="17"/>
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B61, $C$2:$C$712, C61, $D$2:$D$712, D61, $E$2:$E$712, E61) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-    </row>
-    <row r="62" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="6" t="s">
-        <v>62</v>
+    </row>
+    <row r="62" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="3">
+        <v>46287.375</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>107</v>
+        <v>295</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="4">
-        <v>6920</v>
+        <v>1564</v>
       </c>
       <c r="F62" s="4">
-        <v>-2.7543563799999999</v>
+        <v>-9.7883140100000006</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>108</v>
+        <v>297</v>
       </c>
       <c r="H62" s="5">
-        <v>7116</v>
+        <v>1733.7</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" t="str">
+      <c r="J62" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="L62" s="18">
+        <v>3430</v>
+      </c>
+      <c r="M62" s="18">
+        <f>ABS((D62*E62)-L62)</f>
+        <v>302</v>
+      </c>
+      <c r="N62" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B62, $C$2:$C$712, C62, $D$2:$D$712, D62, $E$2:$E$712, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="32">
-        <v>46288.375532407408</v>
-      </c>
-      <c r="B63" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C63" s="33" t="s">
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+    </row>
+    <row r="63" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="3">
+        <v>46254.375</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="4">
+        <v>7</v>
+      </c>
+      <c r="E63" s="4">
+        <v>2230</v>
+      </c>
+      <c r="F63" s="4">
+        <v>-9.898989899</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H63" s="5">
+        <v>2475</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J63" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$712, B63, $C$2:$C$712, C63, $D$2:$D$712, D63, $E$2:$E$712, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="34">
-        <v>887</v>
-      </c>
-      <c r="F63" s="4">
-        <v>-2.74122807</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H63" s="5">
-        <v>912</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J63" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="K63" s="29" t="s">
-        <v>316</v>
-      </c>
-      <c r="L63" s="29">
-        <v>9170</v>
-      </c>
-      <c r="M63" s="29">
-        <f>ABS((D63*E63)-L63)</f>
-        <v>300</v>
-      </c>
-      <c r="N63" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$712, B63, $C$2:$C$712, C63, $D$2:$D$712, D63, $E$2:$E$712, E63) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-      <c r="O63" s="31"/>
-      <c r="P63" s="31"/>
-    </row>
-    <row r="64" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="32">
-        <v>46288.375567129631</v>
-      </c>
-      <c r="B64" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C64" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="34">
-        <v>10</v>
-      </c>
-      <c r="E64" s="34">
-        <v>887</v>
+      <c r="D64" s="4">
+        <v>100</v>
+      </c>
+      <c r="E64" s="4">
+        <v>111</v>
       </c>
       <c r="F64" s="4">
-        <v>-2.74122807</v>
+        <v>-11.02204409</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="H64" s="5">
-        <v>912</v>
+        <v>124.75</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J64" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="K64" s="29" t="s">
-        <v>317</v>
-      </c>
-      <c r="L64" s="29">
-        <v>9070</v>
-      </c>
-      <c r="M64" s="29">
-        <f>ABS((D64*E64)-L64)</f>
-        <v>200</v>
-      </c>
-      <c r="N64" s="31" t="str">
+      <c r="J64" s="72"/>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B64, $C$2:$C$712, C64, $D$2:$D$712, D64, $E$2:$E$712, E64) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-    </row>
-    <row r="65" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D65" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E65" s="4">
-        <v>3830</v>
+        <v>561</v>
       </c>
       <c r="F65" s="4">
-        <v>-2.3955147810000001</v>
+        <v>-11.67440762</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="H65" s="5">
-        <v>3924</v>
+        <v>635.15</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J65" s="51"/>
+      <c r="J65" s="72" t="s">
+        <v>41</v>
+      </c>
       <c r="K65" s="17"/>
       <c r="L65" s="17"/>
       <c r="M65" s="17"/>
@@ -4346,40 +4444,36 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B65, $C$2:$C$712, C65, $D$2:$D$712, D65, $E$2:$E$712, E65) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-    </row>
-    <row r="66" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="3">
-        <v>46252.6875</v>
+    </row>
+    <row r="66" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D66" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E66" s="4">
-        <v>122</v>
+        <v>4164</v>
       </c>
       <c r="F66" s="4">
-        <v>-2.2044088180000001</v>
+        <v>-11.90098381</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H66" s="5">
-        <v>124.75</v>
+        <v>4726.5</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="52" t="s">
-        <v>41</v>
-      </c>
+      <c r="J66" s="72"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
@@ -4387,86 +4481,77 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B66, $C$2:$C$712, C66, $D$2:$D$712, D66, $E$2:$E$712, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O66" s="10"/>
-      <c r="P66" s="10"/>
-    </row>
-    <row r="67" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O66"/>
+      <c r="P66"/>
+    </row>
+    <row r="67" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
-        <v>46287.375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="4">
-        <v>19300</v>
+        <v>2892</v>
       </c>
       <c r="F67" s="4">
-        <v>-1.905972046</v>
+        <v>-14.15850401</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H67" s="5">
-        <v>19675</v>
+        <v>3369</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K67" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="L67" s="18">
-        <v>19950</v>
-      </c>
-      <c r="M67" s="18">
-        <f>ABS((D67*E67)-L67)</f>
-        <v>650</v>
-      </c>
-      <c r="N67" s="10" t="str">
+      <c r="J67" s="72"/>
+      <c r="K67" s="17"/>
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B67, $C$2:$C$712, C67, $D$2:$D$712, D67, $E$2:$E$712, E67) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O67"/>
+      <c r="P67"/>
+    </row>
+    <row r="68" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D68" s="4">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="E68" s="4">
-        <v>31.01</v>
+        <v>4014</v>
       </c>
       <c r="F68" s="4">
-        <v>-1.836024058</v>
+        <v>-15.0745795</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="H68" s="5">
-        <v>31.59</v>
+        <v>4726.5</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="51" t="s">
-        <v>55</v>
-      </c>
+      <c r="J68" s="72"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
@@ -4474,38 +4559,40 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B68, $C$2:$C$712, C68, $D$2:$D$712, D68, $E$2:$E$712, E68) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O68" s="30"/>
+      <c r="O68"/>
       <c r="P68"/>
     </row>
-    <row r="69" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" s="26" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D69" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" s="4">
-        <v>3856</v>
+        <v>701</v>
       </c>
       <c r="F69" s="4">
-        <v>-1.7329255859999999</v>
+        <v>-15.74519231</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="H69" s="5">
-        <v>3924</v>
+        <v>832</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="51"/>
+      <c r="J69" s="72" t="s">
+        <v>41</v>
+      </c>
       <c r="K69" s="17"/>
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
@@ -4513,181 +4600,179 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B69, $C$2:$C$712, C69, $D$2:$D$712, D69, $E$2:$E$712, E69) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O69" s="19"/>
-      <c r="P69" s="10"/>
-    </row>
-    <row r="70" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="3">
-        <v>46261.375</v>
+      <c r="O69"/>
+      <c r="P69"/>
+    </row>
+    <row r="70" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D70" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E70" s="4">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F70" s="4">
-        <v>-1.157184185</v>
+        <v>-16.913946589999998</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H70" s="5">
-        <v>207.4</v>
+        <v>235.9</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J70" s="18" t="s">
+      <c r="J70" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="K70" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="L70" s="18">
-        <v>10550</v>
-      </c>
-      <c r="M70" s="18">
-        <f>ABS((D70*E70)-L70)</f>
-        <v>300</v>
-      </c>
-      <c r="N70" s="10" t="str">
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
+      <c r="M70" s="17"/>
+      <c r="N70" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B70, $C$2:$C$712, C70, $D$2:$D$712, D70, $E$2:$E$712, E70) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="3">
-        <v>46282.443055555559</v>
+        <v>Unique</v>
+      </c>
+      <c r="O70"/>
+      <c r="P70"/>
+    </row>
+    <row r="71" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D71" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E71" s="4">
-        <v>205</v>
+        <v>3914</v>
       </c>
       <c r="F71" s="4">
-        <v>-1.157184185</v>
+        <v>-17.19030995</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H71" s="5">
-        <v>207.4</v>
+        <v>4726.5</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J71" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K71" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="L71" s="18">
-        <v>10550</v>
-      </c>
-      <c r="M71" s="18">
-        <f>ABS((D71*E71)-L71)</f>
-        <v>300</v>
-      </c>
+      <c r="J71" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17"/>
       <c r="N71" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B71, $C$2:$C$712, C71, $D$2:$D$712, D71, $E$2:$E$712, E71) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="3">
-        <v>46031.4375</v>
+        <v>Unique</v>
+      </c>
+      <c r="O71"/>
+      <c r="P71"/>
+    </row>
+    <row r="72" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" s="4">
-        <v>1052</v>
+        <v>2752</v>
       </c>
       <c r="F72" s="4">
-        <v>-0.94161958570000004</v>
+        <v>-18.314039770000001</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>221</v>
+        <v>93</v>
       </c>
       <c r="H72" s="5">
-        <v>1062</v>
+        <v>3369</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="18" t="s">
+      <c r="J72" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="M72" s="18">
-        <f>ABS((D72*E72)-L72)</f>
-        <v>3156</v>
-      </c>
-      <c r="N72" s="10" t="str">
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
+      <c r="N72" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B72, $C$2:$C$712, C72, $D$2:$D$712, D72, $E$2:$E$712, E72) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P72" s="19"/>
-    </row>
-    <row r="73" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="6" t="s">
-        <v>62</v>
+      <c r="O72"/>
+      <c r="P72"/>
+    </row>
+    <row r="73" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="3">
+        <v>46281.416666666664</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>49</v>
+        <v>285</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D73" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
-        <v>3888</v>
+        <v>726</v>
       </c>
       <c r="F73" s="4">
-        <v>-0.91743119269999995</v>
+        <v>-20.316101419999999</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>50</v>
+        <v>292</v>
       </c>
       <c r="H73" s="5">
-        <v>3924</v>
+        <v>911.1</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J73" s="51"/>
-      <c r="K73" s="17"/>
-      <c r="L73" s="17"/>
-      <c r="M73" s="17"/>
-      <c r="N73" t="str">
+      <c r="J73" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="K73" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="L73" s="18">
+        <v>17940</v>
+      </c>
+      <c r="M73" s="18">
+        <f>ABS((D73*E73)-L73)</f>
+        <v>10680</v>
+      </c>
+      <c r="N73" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B73, $C$2:$C$712, C73, $D$2:$D$712, D73, $E$2:$E$712, E73) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O73" s="26"/>
-    </row>
-    <row r="74" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>46268.375</v>
       </c>
@@ -4733,37 +4818,35 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="75" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D75" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E75" s="4">
-        <v>281</v>
+        <v>2660</v>
       </c>
       <c r="F75" s="4">
-        <v>0.7529580495</v>
+        <v>-21.044820420000001</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H75" s="5">
-        <v>278.89999999999998</v>
+        <v>3369</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J75" s="51" t="s">
-        <v>41</v>
-      </c>
+      <c r="J75" s="72"/>
       <c r="K75" s="17"/>
       <c r="L75" s="17"/>
       <c r="M75" s="17"/>
@@ -4771,63 +4854,56 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B75, $C$2:$C$712, C75, $D$2:$D$712, D75, $E$2:$E$712, E75) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O75" s="10"/>
-      <c r="P75" s="26"/>
-    </row>
-    <row r="76" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O75"/>
+      <c r="P75"/>
+    </row>
+    <row r="76" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
-        <v>46275.457638888889</v>
+        <v>46252.688194444447</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D76" s="4">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E76" s="4">
-        <v>222</v>
+        <v>136.15</v>
       </c>
       <c r="F76" s="4">
-        <v>0.77624948930000004</v>
+        <v>-21.30057803</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="H76" s="5">
-        <v>220.29</v>
+        <v>173</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J76" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K76" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="L76" s="18">
-        <v>56375</v>
-      </c>
-      <c r="M76" s="18">
-        <f>ABS((D76*E76)-L76)</f>
-        <v>34175</v>
-      </c>
-      <c r="N76" s="10" t="str">
+      <c r="J76" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="K76" s="17"/>
+      <c r="L76" s="17"/>
+      <c r="M76" s="17"/>
+      <c r="N76" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B76, $C$2:$C$712, C76, $D$2:$D$712, D76, $E$2:$E$712, E76) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O76" s="10"/>
-      <c r="P76" s="10"/>
-    </row>
-    <row r="77" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O76"/>
+      <c r="P76"/>
+    </row>
+    <row r="77" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3">
-        <v>46252.645138888889</v>
+        <v>46281.416666666664</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>68</v>
+        <v>285</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>10</v>
@@ -4836,32 +4912,39 @@
         <v>10</v>
       </c>
       <c r="E77" s="4">
-        <v>401</v>
+        <v>706</v>
       </c>
       <c r="F77" s="4">
-        <v>0.98212037269999997</v>
+        <v>-22.511250140000001</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>69</v>
+        <v>292</v>
       </c>
       <c r="H77" s="5">
-        <v>397.1</v>
+        <v>911.1</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J77" s="53" t="s">
+      <c r="J77" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
-      <c r="M77" s="17"/>
-      <c r="N77" t="str">
+      <c r="K77" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="L77" s="18">
+        <v>17940</v>
+      </c>
+      <c r="M77" s="18">
+        <f>ABS((D77*E77)-L77)</f>
+        <v>10880</v>
+      </c>
+      <c r="N77" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B77, $C$2:$C$712, C77, $D$2:$D$712, D77, $E$2:$E$712, E77) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3">
         <v>46286.375694444447</v>
       </c>
@@ -4908,7 +4991,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="79" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>46287.375</v>
       </c>
@@ -4956,7 +5039,7 @@
       <c r="O79" s="10"/>
       <c r="P79" s="10"/>
     </row>
-    <row r="80" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3">
         <v>46267.461111111108</v>
       </c>
@@ -5002,7 +5085,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="32">
         <v>46281.443055555559</v>
       </c>
@@ -5052,7 +5135,7 @@
       </c>
       <c r="P81" s="31"/>
     </row>
-    <row r="82" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="32">
         <v>46281.388888888891</v>
       </c>
@@ -5102,7 +5185,7 @@
       </c>
       <c r="P82" s="31"/>
     </row>
-    <row r="83" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
         <v>46286.468055555553</v>
       </c>
@@ -5148,7 +5231,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3">
         <v>46267.375</v>
       </c>
@@ -5195,7 +5278,7 @@
       </c>
       <c r="P84" s="26"/>
     </row>
-    <row r="85" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>46274.375</v>
       </c>
@@ -5245,36 +5328,36 @@
       </c>
       <c r="P85" s="10"/>
     </row>
-    <row r="86" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D86" s="4">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E86" s="4">
-        <v>2435</v>
+        <v>2560</v>
       </c>
       <c r="F86" s="4">
-        <v>2.3109243699999999</v>
+        <v>-24.01306026</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H86" s="5">
-        <v>2380</v>
+        <v>3369</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J86" s="51" t="s">
-        <v>55</v>
+      <c r="J86" s="72" t="s">
+        <v>41</v>
       </c>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
@@ -5283,54 +5366,56 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B86, $C$2:$C$712, C86, $D$2:$D$712, D86, $E$2:$E$712, E86) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="3">
+      <c r="O86"/>
+      <c r="P86"/>
+    </row>
+    <row r="87" spans="1:16" s="67" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="61">
         <v>46281.376388888886</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="4">
+      <c r="C87" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="63">
         <v>1</v>
       </c>
-      <c r="E87" s="4">
+      <c r="E87" s="63">
         <v>4940</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="63">
         <v>2.553456508</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="H87" s="5">
+      <c r="H87" s="65">
         <v>4817</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J87" s="18" t="s">
+      <c r="I87" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J87" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="K87" s="18" t="s">
+      <c r="K87" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="L87" s="18">
+      <c r="L87" s="66">
         <v>4640</v>
       </c>
-      <c r="M87" s="18">
+      <c r="M87" s="66">
         <f>ABS((D87*E87)-L87)</f>
         <v>300</v>
       </c>
-      <c r="N87" s="10" t="str">
+      <c r="N87" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B87, $C$2:$C$712, C87, $D$2:$D$712, D87, $E$2:$E$712, E87) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="3">
         <v>46267.375</v>
       </c>
@@ -5376,7 +5461,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>46275.375</v>
       </c>
@@ -5422,7 +5507,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="11">
         <v>46273.375</v>
       </c>
@@ -5471,46 +5556,44 @@
         <v>243</v>
       </c>
     </row>
-    <row r="91" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="8" t="s">
+    <row r="91" spans="1:16" s="67" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="8">
+      <c r="C91" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="68">
         <v>15</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="68">
         <v>1090</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="63">
         <v>2.8301886789999999</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="H91" s="5">
+      <c r="H91" s="65">
         <v>1060</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="36"/>
-      <c r="K91" s="18"/>
-      <c r="L91" s="18"/>
-      <c r="M91" s="18"/>
-      <c r="N91" s="10" t="str">
+      <c r="I91" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="69"/>
+      <c r="K91" s="66"/>
+      <c r="L91" s="66"/>
+      <c r="M91" s="66"/>
+      <c r="N91" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B91, $C$2:$C$712, C91, $D$2:$D$712, D91, $E$2:$E$712, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O91" s="10"/>
-      <c r="P91" s="10"/>
-    </row>
-    <row r="92" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="32">
         <v>46267.375</v>
       </c>
@@ -5558,7 +5641,7 @@
       <c r="O92" s="10"/>
       <c r="P92" s="10"/>
     </row>
-    <row r="93" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="32">
         <v>46267.375</v>
       </c>
@@ -5606,53 +5689,53 @@
       <c r="O93" s="10"/>
       <c r="P93" s="10"/>
     </row>
-    <row r="94" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="3">
+    <row r="94" spans="1:16" s="67" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="61">
         <v>46280.435416666667</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" s="4">
+      <c r="C94" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="63">
         <v>50</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E94" s="63">
         <v>409</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="63">
         <v>2.9967262649999999</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G94" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="H94" s="5">
+      <c r="H94" s="65">
         <v>397.1</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="18" t="s">
+      <c r="I94" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="K94" s="18" t="s">
+      <c r="K94" s="66" t="s">
         <v>282</v>
       </c>
-      <c r="L94" s="18">
+      <c r="L94" s="66">
         <v>39300</v>
       </c>
-      <c r="M94" s="18">
+      <c r="M94" s="66">
         <f>ABS((D94*E94)-L94)</f>
         <v>18850</v>
       </c>
-      <c r="N94" s="10" t="str">
+      <c r="N94" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B94, $C$2:$C$712, C94, $D$2:$D$712, D94, $E$2:$E$712, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="42">
         <v>46273.375</v>
       </c>
@@ -5702,7 +5785,7 @@
       </c>
       <c r="P95" s="31"/>
     </row>
-    <row r="96" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="32">
         <v>46274.375</v>
       </c>
@@ -5752,7 +5835,7 @@
       </c>
       <c r="P96" s="31"/>
     </row>
-    <row r="97" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
         <v>46275.375</v>
       </c>
@@ -5798,53 +5881,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="3">
+    <row r="98" spans="1:16" s="67" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="61">
         <v>46267.38958333333</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="4">
+      <c r="C98" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="63">
         <v>100</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E98" s="63">
         <v>344</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="63">
         <v>3.4586466169999999</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="H98" s="5">
+      <c r="H98" s="65">
         <v>332.5</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J98" s="18" t="s">
+      <c r="I98" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J98" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="K98" s="18" t="s">
+      <c r="K98" s="66" t="s">
         <v>225</v>
       </c>
-      <c r="L98" s="18">
+      <c r="L98" s="66">
         <v>33200</v>
       </c>
-      <c r="M98" s="18">
+      <c r="M98" s="66">
         <f>ABS((D98*E98)-L98)</f>
         <v>1200</v>
       </c>
-      <c r="N98" s="10" t="str">
+      <c r="N98" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B98, $C$2:$C$712, C98, $D$2:$D$712, D98, $E$2:$E$712, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="32">
         <v>46267.425694444442</v>
       </c>
@@ -5894,7 +5977,7 @@
       </c>
       <c r="P99" s="31"/>
     </row>
-    <row r="100" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="32">
         <v>46280.593055555553</v>
       </c>
@@ -5944,35 +6027,35 @@
       </c>
       <c r="P100" s="31"/>
     </row>
-    <row r="101" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D101" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E101" s="4">
-        <v>2470</v>
+        <v>660</v>
       </c>
       <c r="F101" s="4">
-        <v>3.7815126050000001</v>
+        <v>-29.415539280000001</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="H101" s="5">
-        <v>2380</v>
+        <v>935.05</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="51" t="s">
+      <c r="J101" s="72" t="s">
         <v>41</v>
       </c>
       <c r="K101" s="17"/>
@@ -5982,9 +6065,10 @@
         <f>IF(COUNTIFS( $B$2:$B$712, B101, $C$2:$C$712, C101, $D$2:$D$712, D101, $E$2:$E$712, E101) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P101" s="25"/>
-    </row>
-    <row r="102" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O101"/>
+      <c r="P101"/>
+    </row>
+    <row r="102" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="11">
         <v>46273.375</v>
       </c>
@@ -6030,7 +6114,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
         <v>46276.375</v>
       </c>
@@ -6076,7 +6160,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="104" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3">
         <v>46267.375</v>
       </c>
@@ -6126,7 +6210,7 @@
       </c>
       <c r="P104" s="10"/>
     </row>
-    <row r="105" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6173,43 +6257,46 @@
       </c>
       <c r="P105"/>
     </row>
-    <row r="106" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="8" t="s">
+    <row r="106" spans="1:16" s="67" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C106" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D106" s="8">
+      <c r="C106" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="68">
         <v>10</v>
       </c>
-      <c r="E106" s="12">
+      <c r="E106" s="68">
         <v>773</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="63">
         <v>4.3466522679999997</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="G106" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="H106" s="5">
+      <c r="H106" s="65">
         <v>740.8</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J106" s="36" t="s">
+      <c r="I106" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J106" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="N106" s="10" t="str">
+      <c r="K106" s="66"/>
+      <c r="L106" s="66"/>
+      <c r="M106" s="66"/>
+      <c r="N106" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B106, $C$2:$C$712, C106, $D$2:$D$712, D106, $E$2:$E$712, E106) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -6255,7 +6342,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>46288.430034722223</v>
       </c>
@@ -6301,7 +6388,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="109" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -6348,7 +6435,7 @@
       </c>
       <c r="O109"/>
     </row>
-    <row r="110" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3">
         <v>46267.375</v>
       </c>
@@ -6395,7 +6482,7 @@
       </c>
       <c r="P110" s="19"/>
     </row>
-    <row r="111" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
         <v>46261.375</v>
       </c>
@@ -6441,7 +6528,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6475,53 +6562,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="3">
+    <row r="113" spans="1:16" s="67" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="61">
         <v>46276.375</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B113" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D113" s="4">
+      <c r="C113" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="63">
         <v>25</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E113" s="63">
         <v>360</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="63">
         <v>5.263157895</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="G113" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="H113" s="5">
+      <c r="H113" s="65">
         <v>342</v>
       </c>
-      <c r="I113" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J113" s="18" t="s">
+      <c r="I113" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J113" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="K113" s="18" t="s">
+      <c r="K113" s="66" t="s">
         <v>277</v>
       </c>
-      <c r="L113" s="18">
+      <c r="L113" s="66">
         <v>8700</v>
       </c>
-      <c r="M113" s="18">
+      <c r="M113" s="66">
         <f>ABS((D113*E113)-L113)</f>
         <v>300</v>
       </c>
-      <c r="N113" s="10" t="str">
+      <c r="N113" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B113, $C$2:$C$712, C113, $D$2:$D$712, D113, $E$2:$E$712, E113) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46274.375</v>
       </c>
@@ -6567,7 +6654,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -6613,7 +6700,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -6662,7 +6749,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -6708,7 +6795,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3">
         <v>46274.375</v>
       </c>
@@ -6754,7 +6841,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="119" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -6803,7 +6890,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="120" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6852,55 +6939,53 @@
         <v>243</v>
       </c>
     </row>
-    <row r="121" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="3">
+    <row r="121" spans="1:16" s="67" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="61">
         <v>46262.375</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D121" s="4">
+      <c r="C121" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="63">
         <v>2</v>
       </c>
-      <c r="E121" s="4">
+      <c r="E121" s="63">
         <v>4360</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="63">
         <v>5.6790362849999996</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="G121" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="H121" s="5">
+      <c r="H121" s="65">
         <v>4125.7</v>
       </c>
-      <c r="I121" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J121" s="18" t="s">
+      <c r="I121" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J121" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="K121" s="18" t="s">
+      <c r="K121" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="L121" s="18">
+      <c r="L121" s="66">
         <v>8420</v>
       </c>
-      <c r="M121" s="18">
+      <c r="M121" s="66">
         <f>ABS((D121*E121)-L121)</f>
         <v>300</v>
       </c>
-      <c r="N121" s="10" t="str">
+      <c r="N121" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B121, $C$2:$C$712, C121, $D$2:$D$712, D121, $E$2:$E$712, E121) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O121" s="10"/>
-      <c r="P121" s="10"/>
-    </row>
-    <row r="122" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="122" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>46261.375</v>
       </c>
@@ -6948,7 +7033,7 @@
       <c r="O122"/>
       <c r="P122" s="10"/>
     </row>
-    <row r="123" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
         <v>46253.375</v>
       </c>
@@ -6991,7 +7076,7 @@
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
     </row>
-    <row r="124" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="11">
         <v>46243.375</v>
       </c>
@@ -7040,7 +7125,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -7075,7 +7160,7 @@
       </c>
       <c r="O125" s="25"/>
     </row>
-    <row r="126" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -7115,7 +7200,7 @@
       </c>
       <c r="P126"/>
     </row>
-    <row r="127" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3">
         <v>46335.442361111112</v>
       </c>
@@ -7161,7 +7246,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -7210,7 +7295,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="8" t="s">
         <v>62</v>
       </c>
@@ -7246,7 +7331,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -7292,7 +7377,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="32">
         <v>46260.556944444441</v>
       </c>
@@ -7338,7 +7423,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="32">
         <v>46261.375</v>
       </c>
@@ -7384,7 +7469,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7422,55 +7507,54 @@
       </c>
       <c r="P133"/>
     </row>
-    <row r="134" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="11">
+    <row r="134" spans="1:16" s="67" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="70">
         <v>46243.375</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C134" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D134" s="8">
+      <c r="C134" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="68">
         <v>90</v>
       </c>
-      <c r="E134" s="8">
+      <c r="E134" s="68">
         <v>298</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="63">
         <v>6.8483327359999997</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="G134" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="H134" s="5">
+      <c r="H134" s="65">
         <v>278.89999999999998</v>
       </c>
-      <c r="I134" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J134" s="18" t="s">
+      <c r="I134" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J134" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="K134" s="18" t="s">
+      <c r="K134" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="L134" s="18">
+      <c r="L134" s="66">
         <v>26109.000000000004</v>
       </c>
-      <c r="M134" s="29">
+      <c r="M134" s="66">
         <f>ABS((D134*E134)-L134)</f>
         <v>710.99999999999636</v>
       </c>
-      <c r="N134" s="10" t="str">
+      <c r="N134" s="67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B134, $C$2:$C$712, C134, $D$2:$D$712, D134, $E$2:$E$712, E134) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O134" s="10"/>
-      <c r="P134"/>
-    </row>
-    <row r="135" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P134" s="71"/>
+    </row>
+    <row r="135" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46281.375</v>
       </c>
@@ -7520,7 +7604,7 @@
       </c>
       <c r="P135" s="10"/>
     </row>
-    <row r="136" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="3">
         <v>46266.375</v>
       </c>
@@ -7567,7 +7651,7 @@
       </c>
       <c r="P136" s="31"/>
     </row>
-    <row r="137" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -7616,7 +7700,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="32">
         <v>46335.62777777778</v>
       </c>
@@ -7664,7 +7748,7 @@
       <c r="O138" s="31"/>
       <c r="P138" s="31"/>
     </row>
-    <row r="139" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="32">
         <v>46280.375694444447</v>
       </c>
@@ -7712,7 +7796,7 @@
       <c r="O139" s="31"/>
       <c r="P139" s="31"/>
     </row>
-    <row r="140" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -7762,7 +7846,7 @@
       </c>
       <c r="P140" s="10"/>
     </row>
-    <row r="141" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -7808,7 +7892,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46276.4</v>
       </c>
@@ -7854,7 +7938,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -7900,7 +7984,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="32">
         <v>46266.375694444447</v>
       </c>
@@ -7946,55 +8030,53 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="32">
+    <row r="145" spans="1:16" s="26" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="55">
         <v>46267.424305555556</v>
       </c>
-      <c r="B145" s="33" t="s">
+      <c r="B145" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="C145" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D145" s="34">
+      <c r="C145" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" s="57">
         <v>2</v>
       </c>
-      <c r="E145" s="34">
+      <c r="E145" s="57">
         <v>2624</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="57">
         <v>7.3210633950000004</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="G145" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="H145" s="5">
+      <c r="H145" s="59">
         <v>2445</v>
       </c>
-      <c r="I145" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J145" s="29" t="s">
+      <c r="I145" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="J145" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="K145" s="29" t="s">
+      <c r="K145" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="L145" s="29">
+      <c r="L145" s="60">
         <v>4968</v>
       </c>
-      <c r="M145" s="29">
+      <c r="M145" s="60">
         <f>ABS((D145*E145)-L145)</f>
         <v>280</v>
       </c>
-      <c r="N145" s="31" t="str">
+      <c r="N145" s="26" t="str">
         <f>IF(COUNTIFS( $B$2:$B$712, B145, $C$2:$C$712, C145, $D$2:$D$712, D145, $E$2:$E$712, E145) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O145" s="31"/>
-      <c r="P145" s="31"/>
-    </row>
-    <row r="146" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="146" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8029,7 +8111,7 @@
       </c>
       <c r="O146" s="31"/>
     </row>
-    <row r="147" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="11">
         <v>46253.375</v>
       </c>
@@ -8068,7 +8150,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="148" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3">
         <v>46261.375</v>
       </c>
@@ -8115,7 +8197,7 @@
       </c>
       <c r="P148" s="10"/>
     </row>
-    <row r="149" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -8151,7 +8233,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3">
         <v>46262.375</v>
       </c>
@@ -8198,7 +8280,7 @@
       </c>
       <c r="O150" s="31"/>
     </row>
-    <row r="151" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -8247,7 +8329,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="42">
         <v>46243.505555555559</v>
       </c>
@@ -8296,7 +8378,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="153" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="32">
         <v>46280.588194444441</v>
       </c>
@@ -8345,7 +8427,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="154" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46267.375</v>
       </c>
@@ -8393,7 +8475,7 @@
       <c r="O154" s="10"/>
       <c r="P154" s="10"/>
     </row>
-    <row r="155" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -8439,7 +8521,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="156" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="8" t="s">
         <v>62</v>
       </c>
@@ -8475,7 +8557,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="32">
         <v>46258.443055555559</v>
       </c>
@@ -8523,7 +8605,7 @@
       <c r="O157" s="31"/>
       <c r="P157" s="31"/>
     </row>
-    <row r="158" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="32">
         <v>46259.375</v>
       </c>
@@ -8571,7 +8653,7 @@
       <c r="O158" s="31"/>
       <c r="P158" s="31"/>
     </row>
-    <row r="159" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8605,7 +8687,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="160" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3">
         <v>46276.390277777777</v>
       </c>
@@ -8651,7 +8733,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="161" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -8700,7 +8782,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8735,7 +8817,7 @@
       </c>
       <c r="P162" s="31"/>
     </row>
-    <row r="163" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -8784,7 +8866,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="164" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="3">
         <v>46261.375</v>
       </c>
@@ -8832,7 +8914,7 @@
       <c r="O164" s="10"/>
       <c r="P164" s="10"/>
     </row>
-    <row r="165" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3">
         <v>46266.375</v>
       </c>
@@ -8882,7 +8964,7 @@
       </c>
       <c r="P165" s="10"/>
     </row>
-    <row r="166" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -8931,7 +9013,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="32">
         <v>46272.451388888891</v>
       </c>
@@ -8979,7 +9061,7 @@
       <c r="O167" s="31"/>
       <c r="P167" s="31"/>
     </row>
-    <row r="168" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="32">
         <v>46272.390972222223</v>
       </c>
@@ -9027,7 +9109,7 @@
       <c r="O168" s="31"/>
       <c r="P168" s="31"/>
     </row>
-    <row r="169" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="32">
         <v>46258.443749999999</v>
       </c>
@@ -9075,7 +9157,7 @@
       <c r="O169" s="31"/>
       <c r="P169" s="31"/>
     </row>
-    <row r="170" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="42">
         <v>46253.4</v>
       </c>
@@ -9118,7 +9200,7 @@
       <c r="O170" s="31"/>
       <c r="P170" s="31"/>
     </row>
-    <row r="171" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9154,7 +9236,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="172" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="11">
         <v>46252.6875</v>
       </c>
@@ -9190,7 +9272,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="173" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="35">
         <v>46255</v>
       </c>
@@ -9237,7 +9319,7 @@
       </c>
       <c r="P173" s="31"/>
     </row>
-    <row r="174" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="32">
         <v>46261.385416666664</v>
       </c>
@@ -9283,7 +9365,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="175" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="8" t="s">
         <v>62</v>
       </c>
@@ -9317,7 +9399,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="176" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -9367,7 +9449,7 @@
       </c>
       <c r="P176"/>
     </row>
-    <row r="177" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -9403,7 +9485,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="44">
         <v>46273.385416666664</v>
       </c>
@@ -9453,7 +9535,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9489,7 +9571,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="180" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -9535,7 +9617,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="181" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="8" t="s">
         <v>62</v>
       </c>
@@ -9576,7 +9658,7 @@
       <c r="O181" s="10"/>
       <c r="P181" s="10"/>
     </row>
-    <row r="182" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -9624,7 +9706,7 @@
       <c r="O182"/>
       <c r="P182"/>
     </row>
-    <row r="183" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -9670,7 +9752,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="184" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9709,7 +9791,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="185" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3">
         <v>46276.388194444444</v>
       </c>
@@ -9755,7 +9837,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="186" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -9801,7 +9883,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="187" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -9850,7 +9932,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="188" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3">
         <v>46262.375</v>
       </c>
@@ -9896,7 +9978,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="189" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -9942,7 +10024,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="190" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="9" t="s">
         <v>62</v>
       </c>
@@ -9976,7 +10058,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="191" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="45" t="s">
         <v>62</v>
       </c>
@@ -10019,7 +10101,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="192" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10053,7 +10135,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10099,7 +10181,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="194" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10145,7 +10227,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="195" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="8" t="s">
         <v>62</v>
       </c>
@@ -10179,7 +10261,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="196" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -10225,7 +10307,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="197" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10271,7 +10353,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="198" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="8" t="s">
         <v>62</v>
       </c>
@@ -10307,7 +10389,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3">
         <v>46269.375</v>
       </c>
@@ -10353,7 +10435,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="200" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -10400,7 +10482,7 @@
       </c>
       <c r="O200" s="10"/>
     </row>
-    <row r="201" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10436,7 +10518,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -10483,7 +10565,7 @@
       </c>
       <c r="P202" s="31"/>
     </row>
-    <row r="203" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="8" t="s">
         <v>62</v>
       </c>
@@ -10519,7 +10601,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="8" t="s">
         <v>62</v>
       </c>
@@ -10553,7 +10635,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -10599,7 +10681,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="206" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="11">
         <v>46243.375</v>
       </c>
@@ -10646,7 +10728,7 @@
       </c>
       <c r="P206" s="26"/>
     </row>
-    <row r="207" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="3">
         <v>46281.37777777778</v>
       </c>
@@ -10692,7 +10774,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="208" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -10741,7 +10823,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="209" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="8" t="s">
         <v>62</v>
       </c>
@@ -10782,7 +10864,7 @@
       <c r="O209" s="10"/>
       <c r="P209" s="10"/>
     </row>
-    <row r="210" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3">
         <v>46266.375</v>
       </c>
@@ -10828,7 +10910,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="211" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="3">
         <v>46262.375</v>
       </c>
@@ -10874,7 +10956,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="212" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3">
         <v>46276.375</v>
       </c>
@@ -10920,7 +11002,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="8" t="s">
         <v>62</v>
       </c>
@@ -10956,7 +11038,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="214" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="8" t="s">
         <v>62</v>
       </c>
@@ -10992,7 +11074,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="215" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="8" t="s">
         <v>62</v>
       </c>
@@ -11026,7 +11108,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="216" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="8" t="s">
         <v>62</v>
       </c>
@@ -11063,7 +11145,7 @@
       </c>
       <c r="O216" s="31"/>
     </row>
-    <row r="217" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="8" t="s">
         <v>62</v>
       </c>
@@ -11100,7 +11182,7 @@
       </c>
       <c r="O217" s="31"/>
     </row>
-    <row r="218" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -11141,7 +11223,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="219" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -11187,7 +11269,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="220" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="8" t="s">
         <v>62</v>
       </c>
@@ -11223,7 +11305,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="221" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11262,7 +11344,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="222" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="8" t="s">
         <v>62</v>
       </c>
@@ -11299,7 +11381,7 @@
       </c>
       <c r="P222" s="31"/>
     </row>
-    <row r="223" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="3">
         <v>46266.375</v>
       </c>
@@ -11349,7 +11431,7 @@
       </c>
       <c r="P223" s="31"/>
     </row>
-    <row r="224" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="3">
         <v>46274.375</v>
       </c>
@@ -11395,7 +11477,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="225" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="11">
         <v>46252.6875</v>
       </c>
@@ -11431,7 +11513,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="226" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>62</v>
       </c>
@@ -11467,7 +11549,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -11514,7 +11596,7 @@
       </c>
       <c r="P227" s="31"/>
     </row>
-    <row r="228" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="3">
         <v>46276.375</v>
       </c>
@@ -11560,7 +11642,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="229" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="8" t="s">
         <v>62</v>
       </c>
@@ -11594,7 +11676,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="230" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="11">
         <v>46252.6875</v>
       </c>
@@ -11630,7 +11712,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="231" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="3">
         <v>46268.375</v>
       </c>
@@ -11676,7 +11758,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="232" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="8" t="s">
         <v>62</v>
       </c>
@@ -11712,7 +11794,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="233" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="8" t="s">
         <v>62</v>
       </c>
@@ -11746,7 +11828,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="234" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="8" t="s">
         <v>62</v>
       </c>
@@ -11780,7 +11862,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="235" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11826,7 +11908,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="236" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="11">
         <v>46252.6875</v>
       </c>
@@ -11862,7 +11944,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="237" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="8" t="s">
         <v>62</v>
       </c>
@@ -11896,7 +11978,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="238" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="11">
         <v>46252.6875</v>
       </c>
@@ -11932,7 +12014,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="239" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -11981,7 +12063,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="240" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="8" t="s">
         <v>62</v>
       </c>
@@ -12015,7 +12097,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="241" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="3">
         <v>46260.375</v>
       </c>
@@ -12062,7 +12144,7 @@
       </c>
       <c r="P241" s="31"/>
     </row>
-    <row r="242" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -12108,7 +12190,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="243" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="8" t="s">
         <v>62</v>
       </c>
@@ -12142,7 +12224,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="244" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="8" t="s">
         <v>62</v>
       </c>
@@ -12178,7 +12260,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="245" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="3">
         <v>46260.375</v>
       </c>
@@ -12224,7 +12306,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="246" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -12270,7 +12352,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="247" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="8" t="s">
         <v>62</v>
       </c>
@@ -12311,7 +12393,7 @@
       <c r="O247" s="10"/>
       <c r="P247" s="10"/>
     </row>
-    <row r="248" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="8" t="s">
         <v>62</v>
       </c>
@@ -12352,7 +12434,7 @@
       <c r="O248" s="10"/>
       <c r="P248" s="10"/>
     </row>
-    <row r="249" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="3">
         <v>46262.375</v>
       </c>
@@ -12399,7 +12481,7 @@
       </c>
       <c r="P249" s="31"/>
     </row>
-    <row r="250" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="8" t="s">
         <v>62</v>
       </c>
@@ -12433,7 +12515,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="251" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="11">
         <v>46252.6875</v>
       </c>
@@ -12470,7 +12552,7 @@
       </c>
       <c r="O251" s="31"/>
     </row>
-    <row r="252" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="3">
         <v>46259.375</v>
       </c>
@@ -12517,7 +12599,7 @@
       </c>
       <c r="O252" s="31"/>
     </row>
-    <row r="253" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="8" t="s">
         <v>62</v>
       </c>
@@ -12553,7 +12635,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="254" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="8" t="s">
         <v>62</v>
       </c>
@@ -12589,7 +12671,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="255" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="8" t="s">
         <v>62</v>
       </c>
@@ -12623,7 +12705,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="256" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -12669,7 +12751,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="257" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="3">
         <v>46266.375</v>
       </c>
@@ -12715,7 +12797,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="258" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="8" t="s">
         <v>62</v>
       </c>
@@ -12749,7 +12831,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="259" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>62</v>
       </c>
@@ -12783,7 +12865,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="260" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="3">
         <v>46262.375</v>
       </c>
@@ -12831,7 +12913,7 @@
       <c r="O260" s="10"/>
       <c r="P260" s="10"/>
     </row>
-    <row r="261" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -12877,7 +12959,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="262" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="8" t="s">
         <v>62</v>
       </c>
@@ -12912,7 +12994,7 @@
       </c>
       <c r="O262" s="31"/>
     </row>
-    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12946,7 +13028,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="264" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="3">
         <v>46261.375</v>
       </c>
@@ -12994,7 +13076,7 @@
       <c r="O264" s="10"/>
       <c r="P264" s="10"/>
     </row>
-    <row r="265" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="8" t="s">
         <v>62</v>
       </c>
@@ -13030,7 +13112,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="266" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="20">
         <v>46255</v>
       </c>
@@ -13076,7 +13158,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="267" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="8" t="s">
         <v>62</v>
       </c>
@@ -13110,7 +13192,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="268" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="8" t="s">
         <v>62</v>
       </c>
@@ -13144,7 +13226,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="269" spans="1:16" s="31" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:16" s="31" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -13182,7 +13264,7 @@
       </c>
       <c r="P269" s="10"/>
     </row>
-    <row r="270" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="8" t="s">
         <v>62</v>
       </c>
@@ -13221,7 +13303,7 @@
       <c r="O270" s="10"/>
       <c r="P270" s="10"/>
     </row>
-    <row r="271" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -13267,7 +13349,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="272" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -13313,7 +13395,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="273" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="8" t="s">
         <v>62</v>
       </c>
@@ -13352,7 +13434,7 @@
       <c r="O273" s="10"/>
       <c r="P273" s="10"/>
     </row>
-    <row r="274" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -13399,7 +13481,7 @@
       </c>
       <c r="P274" s="31"/>
     </row>
-    <row r="275" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="3">
         <v>46260.375</v>
       </c>
@@ -13445,7 +13527,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="276" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="8" t="s">
         <v>62</v>
       </c>
@@ -13486,7 +13568,7 @@
       <c r="O276" s="10"/>
       <c r="P276" s="10"/>
     </row>
-    <row r="277" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="8" t="s">
         <v>62</v>
       </c>
@@ -13524,7 +13606,7 @@
       </c>
       <c r="O277" s="10"/>
     </row>
-    <row r="278" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -13570,7 +13652,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="279" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="11">
         <v>46252.6875</v>
       </c>
@@ -13606,7 +13688,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="280" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13640,7 +13722,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="281" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="11">
         <v>46252.6875</v>
       </c>
@@ -13676,7 +13758,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="282" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="8" t="s">
         <v>62</v>
       </c>
@@ -13711,7 +13793,7 @@
       </c>
       <c r="P282" s="31"/>
     </row>
-    <row r="283" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="11">
         <v>46252.6875</v>
       </c>
@@ -13747,7 +13829,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="284" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="8" t="s">
         <v>62</v>
       </c>
@@ -13781,7 +13863,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="285" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -13827,7 +13909,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="286" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -13873,7 +13955,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="287" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="8" t="s">
         <v>62</v>
       </c>
@@ -13907,7 +13989,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="288" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
         <v>62</v>
       </c>
@@ -13943,7 +14025,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="289" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -13979,7 +14061,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="290" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="8" t="s">
         <v>62</v>
       </c>
@@ -14013,7 +14095,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="291" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="8" t="s">
         <v>62</v>
       </c>
@@ -14047,7 +14129,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="292" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="43" t="s">
         <v>62</v>
       </c>
@@ -14088,7 +14170,7 @@
       <c r="O292" s="31"/>
       <c r="P292" s="31"/>
     </row>
-    <row r="293" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="42">
         <v>46251.506249999999</v>
       </c>
@@ -14127,7 +14209,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="294" spans="1:16" s="31" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:16" s="31" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="8" t="s">
         <v>62</v>
       </c>
@@ -21762,11 +21844,11 @@
   <autoFilter ref="A1:P294" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="S"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P294">
-      <sortCondition ref="F1"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P101">
+      <sortCondition descending="1" ref="F1:F294"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
